--- a/26年10-12月シフト.xlsx
+++ b/26年10-12月シフト.xlsx
@@ -858,9 +858,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S3" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S3" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="T3" s="11" t="inlineStr">
@@ -1008,19 +1008,19 @@
           <t>○</t>
         </is>
       </c>
-      <c r="R4" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="S4" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="R4" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="S4" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="T4" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="U4" s="8" t="inlineStr">
@@ -1057,9 +1057,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC4" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AC4" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AD4" s="8" t="inlineStr">
@@ -1067,9 +1067,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AE4" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AE4" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AF4" s="8" t="inlineStr">
@@ -1134,9 +1134,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K5" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="K5" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="L5" s="8" t="inlineStr">
@@ -1149,9 +1149,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="N5" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="N5" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="O5" s="8">
@@ -1168,9 +1168,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S5" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S5" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="T5" s="8" t="inlineStr">
@@ -1197,9 +1197,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Z5" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z5" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AA5" s="11" t="inlineStr">
@@ -1465,9 +1465,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="R7" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="R7" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="S7" s="8" t="inlineStr">
@@ -1499,9 +1499,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Z7" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="Z7" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AA7" s="8" t="inlineStr">
@@ -1509,14 +1509,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB7" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AC7" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AB7" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="AC7" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AD7" s="8" t="inlineStr">
@@ -1625,9 +1625,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S8" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S8" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="T8" s="8" t="inlineStr">
@@ -1635,9 +1635,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="U8" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="V8" s="8">
@@ -1664,9 +1664,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB8" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AB8" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AC8" s="8" t="inlineStr">
@@ -1679,9 +1679,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="AE8" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AE8" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AF8" s="8" t="inlineStr">
@@ -1746,9 +1746,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K9" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="K9" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="L9" s="8" t="inlineStr">
@@ -1761,9 +1761,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="N9" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="N9" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="O9" s="8">
@@ -1790,9 +1790,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="U9" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="U9" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="V9" s="8">
@@ -1809,9 +1809,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="Z9" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z9" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AA9" s="8" t="inlineStr">
@@ -1834,9 +1834,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AE9" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AE9" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AF9" s="8" t="inlineStr">
@@ -1935,9 +1935,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S10" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S10" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="T10" s="11" t="inlineStr">
@@ -2089,14 +2089,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="R11" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="S11" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="R11" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="S11" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="T11" s="15" t="inlineStr">
@@ -2133,14 +2133,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB11" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AC11" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AB11" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AC11" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AD11" s="15" t="inlineStr">
@@ -2185,9 +2185,9 @@
       </c>
       <c r="C12" s="9" t="inlineStr"/>
       <c r="D12" s="10" t="inlineStr"/>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
@@ -2230,9 +2230,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="N12" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="N12" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="O12" s="8">
@@ -2249,9 +2249,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S12" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S12" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="T12" s="8" t="inlineStr">
@@ -2630,9 +2630,9 @@
       </c>
       <c r="C15" s="9" t="inlineStr"/>
       <c r="D15" s="10" t="inlineStr"/>
-      <c r="E15" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="F15" s="8" t="inlineStr">
@@ -2650,9 +2650,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="I15" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="I15" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="J15" s="8" t="inlineStr">
@@ -2694,14 +2694,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S15" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S15" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="T15" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="U15" s="8" t="inlineStr">
@@ -2733,9 +2733,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB15" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AB15" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AC15" s="8" t="inlineStr">
@@ -2748,9 +2748,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AE15" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AE15" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AF15" s="8" t="inlineStr">
@@ -2799,9 +2799,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="G16" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="G16" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="H16" s="11" t="inlineStr">
@@ -2819,9 +2819,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K16" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="K16" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="L16" s="15" t="inlineStr">
@@ -2843,9 +2843,9 @@
         <f>COUNTIF(E16:N16, "○")</f>
         <v/>
       </c>
-      <c r="Q16" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="Q16" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="R16" s="15" t="inlineStr">
@@ -2853,9 +2853,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S16" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S16" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="T16" s="15" t="inlineStr">
@@ -2892,9 +2892,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB16" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AB16" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AC16" s="15" t="inlineStr">
@@ -2907,9 +2907,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AE16" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AE16" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AF16" s="15" t="inlineStr">
@@ -2998,9 +2998,9 @@
         <f>COUNTIF(E17:N17, "○")</f>
         <v/>
       </c>
-      <c r="Q17" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Q17" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="R17" s="8" t="inlineStr">
@@ -3013,9 +3013,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="T17" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="U17" s="11" t="inlineStr">
@@ -3108,14 +3108,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F18" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="G18" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="G18" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="H18" s="15" t="inlineStr">
@@ -3273,9 +3273,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H19" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="I19" s="8" t="inlineStr">
@@ -3288,9 +3288,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K19" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="K19" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="L19" s="8" t="inlineStr">
@@ -3322,9 +3322,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S19" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S19" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
@@ -3556,14 +3556,14 @@
       </c>
       <c r="C21" s="9" t="inlineStr"/>
       <c r="D21" s="10" t="inlineStr"/>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="F21" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr">
@@ -3620,14 +3620,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S21" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S21" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="T21" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="U21" s="8" t="inlineStr">
@@ -3711,9 +3711,9 @@
       </c>
       <c r="C22" s="9" t="inlineStr"/>
       <c r="D22" s="10" t="inlineStr"/>
-      <c r="E22" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
@@ -3726,9 +3726,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H22" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="H22" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="I22" s="8" t="inlineStr">
@@ -3780,14 +3780,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="T22" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="U22" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="V22" s="8">
@@ -3814,9 +3814,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB22" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AB22" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AC22" s="8" t="inlineStr">
@@ -3829,9 +3829,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AE22" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AE22" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AF22" s="8" t="inlineStr">
@@ -3876,9 +3876,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="G23" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="G23" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
@@ -3886,19 +3886,19 @@
           <t>○</t>
         </is>
       </c>
-      <c r="I23" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="J23" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="K23" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="I23" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="J23" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="K23" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="L23" s="8" t="inlineStr">
@@ -3930,9 +3930,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S23" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S23" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="T23" s="8" t="inlineStr">
@@ -3940,9 +3940,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="U23" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="V23" s="8">
@@ -3969,9 +3969,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB23" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AB23" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AC23" s="8" t="inlineStr">
@@ -3984,9 +3984,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AE23" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AE23" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AF23" s="8" t="inlineStr">
@@ -4041,9 +4041,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="I24" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="I24" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="J24" s="8" t="inlineStr">
@@ -4066,9 +4066,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="N24" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="N24" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="O24" s="8">
@@ -4085,14 +4085,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S24" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S24" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="T24" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="U24" s="8" t="inlineStr">
@@ -4190,9 +4190,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="G25" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="G25" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="H25" s="15" t="inlineStr">
@@ -4225,9 +4225,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="N25" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="N25" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="O25" s="8">
@@ -4350,9 +4350,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H26" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="I26" s="8" t="inlineStr">
@@ -4365,9 +4365,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K26" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="K26" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="L26" s="8" t="inlineStr">
@@ -4697,14 +4697,14 @@
           <t>公</t>
         </is>
       </c>
-      <c r="S28" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T28" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S28" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="U28" s="8" t="inlineStr">
@@ -4952,14 +4952,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F30" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="G30" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="F30" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="G30" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
@@ -4967,9 +4967,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="I30" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="I30" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="J30" s="8" t="inlineStr">
@@ -4977,9 +4977,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K30" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="K30" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="L30" s="8" t="inlineStr">
@@ -5006,9 +5006,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="R30" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="R30" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="S30" s="8" t="inlineStr">
@@ -5016,9 +5016,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="T30" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="U30" s="11" t="inlineStr">
@@ -5050,9 +5050,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB30" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AB30" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AC30" s="11" t="inlineStr">
@@ -5060,9 +5060,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="AD30" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AD30" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AE30" s="8" t="inlineStr">
@@ -5122,9 +5122,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="I31" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="I31" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="J31" s="11" t="inlineStr">
@@ -5147,9 +5147,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="N31" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="N31" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="O31" s="8">
@@ -5166,9 +5166,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S31" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S31" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="T31" s="11" t="inlineStr">
@@ -5176,9 +5176,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="U31" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="V31" s="8">
@@ -5262,14 +5262,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F32" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="G32" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="G32" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
@@ -5287,9 +5287,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K32" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="K32" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="L32" s="11" t="inlineStr">
@@ -5302,9 +5302,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="N32" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="N32" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="O32" s="8">
@@ -5326,14 +5326,14 @@
           <t>公</t>
         </is>
       </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="U32" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="T32" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="V32" s="8">
@@ -5350,9 +5350,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Z32" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="Z32" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AA32" s="8" t="inlineStr">
@@ -5375,9 +5375,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="AE32" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AE32" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AF32" s="8" t="inlineStr">
@@ -5427,19 +5427,19 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H33" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="I33" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="J33" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="H33" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="I33" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="J33" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="K33" s="8" t="inlineStr">
@@ -5457,9 +5457,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="N33" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="N33" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="O33" s="8">
@@ -5476,14 +5476,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S33" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T33" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S33" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="U33" s="11" t="inlineStr">
@@ -5520,14 +5520,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC33" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AD33" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AC33" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AD33" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AE33" s="8" t="inlineStr">
@@ -6432,9 +6432,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S4" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S4" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="T4" s="8" t="inlineStr">
@@ -6442,9 +6442,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="U4" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="U4" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="V4" s="8">
@@ -6704,9 +6704,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K6" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="K6" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="L6" s="15" t="inlineStr">
@@ -6834,9 +6834,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F7" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
@@ -6849,9 +6849,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="I7" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="I7" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="J7" s="8" t="inlineStr">
@@ -6893,9 +6893,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S7" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S7" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="T7" s="8" t="inlineStr">
@@ -6903,9 +6903,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="U7" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="V7" s="8">
@@ -6932,14 +6932,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB7" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AC7" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AB7" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="AC7" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AD7" s="8" t="inlineStr">
@@ -6993,9 +6993,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F8" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="F8" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="G8" s="11" t="inlineStr">
@@ -7003,9 +7003,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="H8" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="H8" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="I8" s="15" t="inlineStr">
@@ -7081,9 +7081,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Z8" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z8" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AA8" s="15" t="inlineStr">
@@ -7091,9 +7091,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB8" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AB8" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AC8" s="15" t="inlineStr">
@@ -7158,14 +7158,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H9" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="I9" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="H9" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="J9" s="8" t="inlineStr">
@@ -7471,9 +7471,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="K11" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="K11" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="L11" s="8" t="inlineStr">
@@ -7505,19 +7505,19 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S11" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T11" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="U11" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S11" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="U11" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="V11" s="8">
@@ -7534,9 +7534,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Z11" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="Z11" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AA11" s="8" t="inlineStr">
@@ -7559,9 +7559,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="AE11" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AE11" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AF11" s="8" t="inlineStr">
@@ -7704,9 +7704,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC12" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AC12" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AD12" s="8" t="inlineStr">
@@ -7714,9 +7714,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AE12" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AE12" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AF12" s="8" t="inlineStr">
@@ -7756,9 +7756,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F13" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
@@ -7781,9 +7781,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K13" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="K13" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="L13" s="8" t="inlineStr">
@@ -7825,9 +7825,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="U13" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="U13" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="V13" s="8">
@@ -7926,9 +7926,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="I14" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="I14" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="J14" s="8" t="inlineStr">
@@ -7936,9 +7936,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K14" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="K14" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="L14" s="11" t="inlineStr">
@@ -8009,14 +8009,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB14" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AC14" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AB14" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="AC14" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AD14" s="8" t="inlineStr">
@@ -8070,9 +8070,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F15" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="G15" s="11" t="inlineStr">
@@ -8080,9 +8080,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="H15" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="H15" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="I15" s="15" t="inlineStr">
@@ -8158,9 +8158,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Z15" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z15" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AA15" s="15" t="inlineStr">
@@ -8168,9 +8168,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB15" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AB15" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AC15" s="15" t="inlineStr">
@@ -8235,14 +8235,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H16" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="I16" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="H16" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="J16" s="8" t="inlineStr">
@@ -8582,14 +8582,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S18" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T18" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S18" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="U18" s="8" t="inlineStr">
@@ -8611,9 +8611,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Z18" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="Z18" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AA18" s="8" t="inlineStr">
@@ -8636,9 +8636,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="AE18" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AE18" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AF18" s="8" t="inlineStr">
@@ -8737,14 +8737,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S19" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S19" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="T19" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="U19" s="8" t="inlineStr">
@@ -8781,9 +8781,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC19" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AC19" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AD19" s="8" t="inlineStr">
@@ -8791,9 +8791,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AE19" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AE19" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AF19" s="8" t="inlineStr">
@@ -8837,9 +8837,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F20" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="F20" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="G20" s="15" t="inlineStr">
@@ -8997,9 +8997,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="G21" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
@@ -9007,9 +9007,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="I21" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="J21" s="8" t="inlineStr">
@@ -9090,14 +9090,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB21" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AC21" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AB21" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="AC21" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AD21" s="8" t="inlineStr">
@@ -9151,19 +9151,19 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F22" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="G22" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="H22" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="F22" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="G22" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="H22" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="I22" s="15" t="inlineStr">
@@ -9181,9 +9181,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="L22" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="L22" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="M22" s="15" t="inlineStr">
@@ -9239,9 +9239,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Z22" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z22" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AA22" s="15" t="inlineStr">
@@ -9249,9 +9249,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB22" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AB22" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AC22" s="15" t="inlineStr">
@@ -9316,14 +9316,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H23" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="I23" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="H23" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="I23" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="J23" s="8" t="inlineStr">
@@ -9761,9 +9761,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H26" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="H26" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="I26" s="8" t="inlineStr">
@@ -9810,14 +9810,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S26" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S26" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="T26" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="U26" s="8" t="inlineStr">
@@ -9906,9 +9906,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F27" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="F27" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="G27" s="8" t="inlineStr">
@@ -9931,9 +9931,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K27" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="K27" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="L27" s="8" t="inlineStr">
@@ -9965,14 +9965,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S27" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T27" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S27" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="U27" s="11" t="inlineStr">
@@ -10115,24 +10115,24 @@
           <t>○</t>
         </is>
       </c>
-      <c r="R28" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="S28" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="U28" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="R28" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="S28" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="T28" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="V28" s="8">
@@ -10216,9 +10216,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F29" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="G29" s="8" t="inlineStr">
@@ -10226,9 +10226,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H29" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="H29" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="I29" s="8" t="inlineStr">
@@ -10241,14 +10241,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K29" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="L29" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="K29" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="L29" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="M29" s="8" t="inlineStr">
@@ -10270,24 +10270,24 @@
           <t>○</t>
         </is>
       </c>
-      <c r="R29" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="S29" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="T29" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="R29" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="S29" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="U29" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="V29" s="8">
@@ -10319,9 +10319,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC29" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AC29" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AD29" s="11" t="inlineStr">
@@ -10329,9 +10329,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="AE29" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AE29" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AF29" s="8" t="inlineStr">
@@ -10430,14 +10430,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S30" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S30" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="T30" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="U30" s="11" t="inlineStr">
@@ -10459,9 +10459,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Z30" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="Z30" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AA30" s="11" t="inlineStr">
@@ -10484,9 +10484,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AE30" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AE30" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AF30" s="8" t="inlineStr">
@@ -11492,14 +11492,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H3" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="I3" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="H3" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="I3" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="J3" s="8" t="inlineStr">
@@ -11541,14 +11541,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S3" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T3" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S3" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="U3" s="8" t="inlineStr">
@@ -11641,9 +11641,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F4" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="F4" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="G4" s="11" t="inlineStr">
@@ -11666,9 +11666,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K4" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="K4" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="L4" s="15" t="inlineStr">
@@ -11811,9 +11811,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="I5" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="I5" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="J5" s="8" t="inlineStr">
@@ -11860,14 +11860,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="U5" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="T5" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="U5" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="V5" s="8">
@@ -11955,9 +11955,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="F6" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="G6" s="15" t="inlineStr">
@@ -11965,9 +11965,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H6" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="H6" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="I6" s="15" t="inlineStr">
@@ -11980,9 +11980,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K6" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="K6" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="L6" s="15" t="inlineStr">
@@ -12014,14 +12014,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S6" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="T6" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S6" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="T6" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="U6" s="15" t="inlineStr">
@@ -12169,9 +12169,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S7" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S7" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="T7" s="8" t="inlineStr">
@@ -12467,9 +12467,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S9" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S9" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="T9" s="8" t="inlineStr">
@@ -12477,9 +12477,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="U9" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="U9" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="V9" s="8">
@@ -12568,14 +12568,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="H10" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H10" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="I10" s="8" t="inlineStr">
@@ -12627,14 +12627,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="T10" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="U10" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="V10" s="8">
@@ -12718,14 +12718,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="G11" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
@@ -12733,9 +12733,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="I11" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="J11" s="8" t="inlineStr">
@@ -12743,9 +12743,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K11" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="K11" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="L11" s="8" t="inlineStr">
@@ -12782,14 +12782,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="U11" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="T11" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="U11" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="V11" s="8">
@@ -12888,9 +12888,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="I12" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="I12" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="J12" s="8" t="inlineStr">
@@ -12932,19 +12932,19 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S12" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="U12" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S12" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="T12" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="U12" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="V12" s="8">
@@ -13032,9 +13032,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F13" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="F13" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="G13" s="15" t="inlineStr">
@@ -13042,9 +13042,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H13" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="H13" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="I13" s="15" t="inlineStr">
@@ -13057,9 +13057,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K13" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="K13" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="L13" s="15" t="inlineStr">
@@ -13544,14 +13544,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S16" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T16" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S16" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="U16" s="8" t="inlineStr">
@@ -13649,14 +13649,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="G17" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="H17" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="G17" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H17" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="I17" s="15" t="inlineStr">
@@ -13799,14 +13799,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="G18" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
@@ -13814,9 +13814,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="I18" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="I18" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="J18" s="8" t="inlineStr">
@@ -13824,9 +13824,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K18" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="K18" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="L18" s="8" t="inlineStr">
@@ -13858,14 +13858,14 @@
           <t>公</t>
         </is>
       </c>
-      <c r="S18" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S18" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="T18" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="U18" s="8" t="inlineStr">
@@ -13954,9 +13954,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F19" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="G19" s="8" t="inlineStr">
@@ -13969,9 +13969,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="I19" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="I19" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="J19" s="8" t="inlineStr">
@@ -14013,9 +14013,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S19" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S19" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
@@ -14023,9 +14023,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="U19" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="V19" s="8">
@@ -14123,9 +14123,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H20" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="H20" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="I20" s="15" t="inlineStr">
@@ -14138,9 +14138,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K20" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="K20" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="L20" s="15" t="inlineStr">
@@ -14625,14 +14625,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S23" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T23" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S23" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="U23" s="8" t="inlineStr">
@@ -14726,14 +14726,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="G24" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="H24" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H24" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="I24" s="8" t="inlineStr">
@@ -14785,14 +14785,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="T24" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="U24" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="V24" s="8">
@@ -14876,14 +14876,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="G25" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="F25" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="G25" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
@@ -14891,9 +14891,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="I25" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="I25" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="J25" s="8" t="inlineStr">
@@ -14901,9 +14901,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K25" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="K25" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="L25" s="8" t="inlineStr">
@@ -15031,9 +15031,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F26" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="G26" s="8" t="inlineStr">
@@ -15046,9 +15046,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="I26" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="I26" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="J26" s="8" t="inlineStr">
@@ -15196,9 +15196,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H27" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="I27" s="8" t="inlineStr">
@@ -15211,9 +15211,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K27" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="K27" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="L27" s="8" t="inlineStr">
@@ -15245,9 +15245,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S27" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S27" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="T27" s="8" t="inlineStr">
@@ -15255,9 +15255,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="U27" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="V27" s="8">

--- a/26年10-12月シフト.xlsx
+++ b/26年10-12月シフト.xlsx
@@ -858,14 +858,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S3" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T3" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S3" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="U3" s="8" t="inlineStr">
@@ -912,9 +912,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AE3" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AE3" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AF3" s="11" t="inlineStr">
@@ -954,19 +954,19 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="G4" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="H4" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H4" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="I4" s="8" t="inlineStr">
@@ -979,9 +979,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K4" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="K4" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="L4" s="8" t="inlineStr">
@@ -1018,14 +1018,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="T4" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="U4" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="U4" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="V4" s="8">
@@ -1042,9 +1042,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Z4" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z4" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AA4" s="8" t="inlineStr">
@@ -1057,9 +1057,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC4" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AC4" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AD4" s="8" t="inlineStr">
@@ -1129,14 +1129,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="J5" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="K5" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="K5" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="L5" s="8" t="inlineStr">
@@ -1168,9 +1168,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S5" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S5" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="T5" s="8" t="inlineStr">
@@ -1197,9 +1197,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Z5" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="Z5" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AA5" s="11" t="inlineStr">
@@ -1411,9 +1411,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
@@ -1426,9 +1426,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="I7" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="J7" s="11" t="inlineStr">
@@ -1470,14 +1470,14 @@
           <t>公</t>
         </is>
       </c>
-      <c r="S7" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T7" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S7" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="U7" s="8" t="inlineStr">
@@ -1509,9 +1509,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB7" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AB7" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AC7" s="8" t="inlineStr">
@@ -1519,14 +1519,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AD7" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AE7" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AD7" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="AE7" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AF7" s="8" t="inlineStr">
@@ -1576,14 +1576,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H8" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="I8" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="I8" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="J8" s="8" t="inlineStr">
@@ -1630,14 +1630,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="U8" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="T8" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="V8" s="8">
@@ -1664,9 +1664,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB8" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AB8" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AC8" s="8" t="inlineStr">
@@ -1674,14 +1674,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AD8" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AE8" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AD8" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AE8" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AF8" s="8" t="inlineStr">
@@ -1716,9 +1716,9 @@
       </c>
       <c r="C9" s="9" t="inlineStr"/>
       <c r="D9" s="10" t="inlineStr"/>
-      <c r="E9" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
@@ -1726,9 +1726,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="G9" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
@@ -1780,14 +1780,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S9" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T9" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S9" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="U9" s="8" t="inlineStr">
@@ -1809,9 +1809,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="Z9" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="Z9" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AA9" s="8" t="inlineStr">
@@ -1824,9 +1824,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC9" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AC9" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AD9" s="8" t="inlineStr">
@@ -1871,14 +1871,14 @@
       </c>
       <c r="C10" s="9" t="inlineStr"/>
       <c r="D10" s="10" t="inlineStr"/>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="F10" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
@@ -1940,14 +1940,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="T10" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="U10" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="V10" s="8">
@@ -2040,14 +2040,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="G11" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="H11" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="G11" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H11" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="I11" s="15" t="inlineStr">
@@ -2094,14 +2094,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S11" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="T11" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S11" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="T11" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="U11" s="15" t="inlineStr">
@@ -2123,9 +2123,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Z11" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z11" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AA11" s="15" t="inlineStr">
@@ -2133,14 +2133,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB11" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AC11" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AB11" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="AC11" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AD11" s="15" t="inlineStr">
@@ -2185,9 +2185,9 @@
       </c>
       <c r="C12" s="9" t="inlineStr"/>
       <c r="D12" s="10" t="inlineStr"/>
-      <c r="E12" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
@@ -2230,9 +2230,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="N12" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="N12" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="O12" s="8">
@@ -2249,14 +2249,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S12" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S12" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="T12" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="U12" s="11" t="inlineStr">
@@ -2635,9 +2635,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="G15" s="8" t="inlineStr">
@@ -2650,9 +2650,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="I15" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="I15" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="J15" s="8" t="inlineStr">
@@ -2694,14 +2694,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S15" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T15" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S15" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="U15" s="8" t="inlineStr">
@@ -2733,14 +2733,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB15" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AC15" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AB15" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AC15" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AD15" s="8" t="inlineStr">
@@ -2794,9 +2794,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F16" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="F16" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="G16" s="11" t="inlineStr">
@@ -2804,9 +2804,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="H16" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="H16" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="I16" s="15" t="inlineStr">
@@ -2848,14 +2848,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="R16" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="S16" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="R16" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="S16" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="T16" s="15" t="inlineStr">
@@ -2944,9 +2944,9 @@
       </c>
       <c r="C17" s="9" t="inlineStr"/>
       <c r="D17" s="10" t="inlineStr"/>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr">
@@ -2964,9 +2964,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="I17" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="J17" s="8" t="inlineStr">
@@ -2998,9 +2998,9 @@
         <f>COUNTIF(E17:N17, "○")</f>
         <v/>
       </c>
-      <c r="Q17" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="Q17" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="R17" s="8" t="inlineStr">
@@ -3013,9 +3013,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="T17" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="U17" s="11" t="inlineStr">
@@ -3052,9 +3052,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC17" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AC17" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AD17" s="8" t="inlineStr">
@@ -3108,9 +3108,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="F18" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="G18" s="15" t="inlineStr">
@@ -3118,9 +3118,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H18" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="H18" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="I18" s="15" t="inlineStr">
@@ -3133,9 +3133,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K18" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="K18" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="L18" s="15" t="inlineStr">
@@ -3148,9 +3148,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="N18" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="N18" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="O18" s="8">
@@ -3162,9 +3162,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="R18" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="R18" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="S18" s="15" t="inlineStr">
@@ -3172,9 +3172,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="T18" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="T18" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="U18" s="15" t="inlineStr">
@@ -3196,9 +3196,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Z18" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z18" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AA18" s="15" t="inlineStr">
@@ -3211,14 +3211,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC18" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AD18" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AC18" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AD18" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AE18" s="15" t="inlineStr">
@@ -3278,9 +3278,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="I19" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="I19" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="J19" s="8" t="inlineStr">
@@ -3288,9 +3288,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K19" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="K19" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="L19" s="8" t="inlineStr">
@@ -3322,9 +3322,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S19" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S19" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
@@ -3556,9 +3556,9 @@
       </c>
       <c r="C21" s="9" t="inlineStr"/>
       <c r="D21" s="10" t="inlineStr"/>
-      <c r="E21" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="F21" s="8" t="inlineStr">
@@ -3601,9 +3601,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="N21" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="N21" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="O21" s="8">
@@ -3615,9 +3615,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="R21" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="R21" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="S21" s="8" t="inlineStr">
@@ -3659,9 +3659,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB21" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AB21" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AC21" s="8" t="inlineStr">
@@ -3669,9 +3669,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AD21" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AD21" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AE21" s="8" t="inlineStr">
@@ -3721,14 +3721,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="G22" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="H22" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="G22" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="I22" s="8" t="inlineStr">
@@ -3775,9 +3775,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S22" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S22" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="T22" s="8" t="inlineStr">
@@ -3785,9 +3785,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="U22" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="V22" s="8">
@@ -3814,9 +3814,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB22" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AB22" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AC22" s="8" t="inlineStr">
@@ -3829,9 +3829,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AE22" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AE22" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AF22" s="8" t="inlineStr">
@@ -3866,19 +3866,19 @@
       </c>
       <c r="C23" s="9" t="inlineStr"/>
       <c r="D23" s="10" t="inlineStr"/>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="G23" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="F23" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
@@ -3891,9 +3891,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="J23" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="J23" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="K23" s="8" t="inlineStr">
@@ -3974,9 +3974,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC23" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AC23" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AD23" s="8" t="inlineStr">
@@ -3984,9 +3984,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AE23" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AE23" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AF23" s="8" t="inlineStr">
@@ -4036,14 +4036,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H24" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="I24" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="H24" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="I24" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="J24" s="8" t="inlineStr">
@@ -4075,9 +4075,9 @@
         <f>COUNTIF(E24:N24, "○")</f>
         <v/>
       </c>
-      <c r="Q24" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Q24" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="R24" s="8" t="inlineStr">
@@ -4185,9 +4185,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F25" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="F25" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="G25" s="15" t="inlineStr">
@@ -4210,14 +4210,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K25" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="L25" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="K25" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="L25" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="M25" s="15" t="inlineStr">
@@ -4225,9 +4225,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="N25" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="N25" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="O25" s="8">
@@ -4239,14 +4239,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="R25" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="S25" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="R25" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="S25" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="T25" s="15" t="inlineStr">
@@ -4288,14 +4288,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC25" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AD25" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AC25" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AD25" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AE25" s="15" t="inlineStr">
@@ -4355,9 +4355,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="I26" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="I26" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="J26" s="8" t="inlineStr">
@@ -4365,9 +4365,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K26" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="K26" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="L26" s="8" t="inlineStr">
@@ -4633,9 +4633,9 @@
       </c>
       <c r="C28" s="9" t="inlineStr"/>
       <c r="D28" s="10" t="inlineStr"/>
-      <c r="E28" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr">
@@ -4678,9 +4678,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="N28" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="N28" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="O28" s="8">
@@ -4736,9 +4736,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB28" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AB28" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AC28" s="8" t="inlineStr">
@@ -4746,9 +4746,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AD28" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AD28" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AE28" s="8" t="inlineStr">
@@ -4802,14 +4802,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="G29" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="H29" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="G29" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="H29" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="I29" s="15" t="inlineStr">
@@ -4856,14 +4856,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S29" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="T29" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S29" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="T29" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="U29" s="15" t="inlineStr">
@@ -4895,9 +4895,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB29" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AB29" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AC29" s="15" t="inlineStr">
@@ -4947,9 +4947,9 @@
       </c>
       <c r="C30" s="9" t="inlineStr"/>
       <c r="D30" s="10" t="inlineStr"/>
-      <c r="E30" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="F30" s="11" t="inlineStr">
@@ -4957,9 +4957,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="G30" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="G30" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
@@ -5006,14 +5006,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="R30" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="S30" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="R30" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="S30" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="T30" s="8" t="inlineStr">
@@ -5050,9 +5050,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB30" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AB30" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AC30" s="11" t="inlineStr">
@@ -5117,9 +5117,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H31" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="H31" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="I31" s="11" t="inlineStr">
@@ -5127,9 +5127,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="J31" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="J31" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="K31" s="8" t="inlineStr">
@@ -5195,9 +5195,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="Z31" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="Z31" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AA31" s="8" t="inlineStr">
@@ -5215,9 +5215,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AD31" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AD31" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AE31" s="8" t="inlineStr">
@@ -5267,9 +5267,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="G32" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="G32" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
@@ -5292,9 +5292,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="L32" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="L32" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="M32" s="8" t="inlineStr">
@@ -5360,9 +5360,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB32" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AB32" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AC32" s="8" t="inlineStr">
@@ -5375,9 +5375,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="AE32" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AE32" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AF32" s="8" t="inlineStr">
@@ -5427,19 +5427,19 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H33" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="I33" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="J33" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="H33" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="I33" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="J33" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="K33" s="8" t="inlineStr">
@@ -5457,9 +5457,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="N33" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="N33" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="O33" s="8">
@@ -5471,14 +5471,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="R33" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="S33" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="R33" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="S33" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="T33" s="8" t="inlineStr">
@@ -5525,9 +5525,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AD33" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AD33" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AE33" s="8" t="inlineStr">
@@ -6368,9 +6368,9 @@
       </c>
       <c r="C4" s="9" t="inlineStr"/>
       <c r="D4" s="10" t="inlineStr"/>
-      <c r="E4" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
@@ -6403,9 +6403,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="L4" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="L4" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="M4" s="8" t="inlineStr">
@@ -6437,14 +6437,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="U4" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="T4" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="V4" s="8">
@@ -6461,9 +6461,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Z4" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z4" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AA4" s="8" t="inlineStr">
@@ -6476,14 +6476,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC4" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AD4" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AC4" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="AD4" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AE4" s="8" t="inlineStr">
@@ -6679,9 +6679,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F6" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="F6" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="G6" s="15" t="inlineStr">
@@ -6704,9 +6704,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K6" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="K6" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="L6" s="15" t="inlineStr">
@@ -6738,14 +6738,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S6" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T6" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S6" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="T6" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="U6" s="15" t="inlineStr">
@@ -6932,9 +6932,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB7" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AB7" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AC7" s="8" t="inlineStr">
@@ -6947,9 +6947,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AE7" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AE7" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AF7" s="8" t="inlineStr">
@@ -6993,9 +6993,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F8" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="G8" s="11" t="inlineStr">
@@ -7003,9 +7003,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="H8" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="I8" s="15" t="inlineStr">
@@ -7081,9 +7081,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Z8" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="Z8" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AA8" s="15" t="inlineStr">
@@ -7091,9 +7091,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB8" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AB8" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AC8" s="15" t="inlineStr">
@@ -7158,9 +7158,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H9" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="I9" s="8" t="inlineStr">
@@ -7173,9 +7173,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K9" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="K9" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="L9" s="8" t="inlineStr">
@@ -7441,9 +7441,9 @@
       </c>
       <c r="C11" s="9" t="inlineStr"/>
       <c r="D11" s="10" t="inlineStr"/>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
@@ -7505,19 +7505,19 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S11" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S11" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="T11" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="U11" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="V11" s="8">
@@ -7534,9 +7534,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Z11" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z11" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AA11" s="8" t="inlineStr">
@@ -7559,9 +7559,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="AE11" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AE11" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AF11" s="8" t="inlineStr">
@@ -7596,9 +7596,9 @@
       </c>
       <c r="C12" s="9" t="inlineStr"/>
       <c r="D12" s="10" t="inlineStr"/>
-      <c r="E12" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
@@ -7641,9 +7641,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="N12" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="N12" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="O12" s="8">
@@ -7756,9 +7756,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="F13" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
@@ -7781,9 +7781,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K13" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="K13" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="L13" s="8" t="inlineStr">
@@ -7796,9 +7796,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="N13" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="N13" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="O13" s="8">
@@ -7820,9 +7820,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="T13" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="U13" s="11" t="inlineStr">
@@ -7970,14 +7970,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S14" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S14" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="T14" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="U14" s="8" t="inlineStr">
@@ -8009,9 +8009,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB14" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AB14" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AC14" s="8" t="inlineStr">
@@ -8024,9 +8024,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AE14" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AE14" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AF14" s="8" t="inlineStr">
@@ -8070,9 +8070,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F15" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="F15" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="G15" s="11" t="inlineStr">
@@ -8080,9 +8080,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="H15" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="I15" s="15" t="inlineStr">
@@ -8158,9 +8158,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Z15" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="Z15" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AA15" s="15" t="inlineStr">
@@ -8168,9 +8168,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB15" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AB15" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AC15" s="15" t="inlineStr">
@@ -8235,9 +8235,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H16" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="I16" s="8" t="inlineStr">
@@ -8250,9 +8250,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K16" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="K16" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="L16" s="8" t="inlineStr">
@@ -8518,9 +8518,9 @@
       </c>
       <c r="C18" s="9" t="inlineStr"/>
       <c r="D18" s="10" t="inlineStr"/>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
@@ -8548,9 +8548,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="K18" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="K18" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="L18" s="8" t="inlineStr">
@@ -8611,9 +8611,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Z18" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z18" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AA18" s="8" t="inlineStr">
@@ -8636,9 +8636,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="AE18" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AE18" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AF18" s="8" t="inlineStr">
@@ -8673,9 +8673,9 @@
       </c>
       <c r="C19" s="9" t="inlineStr"/>
       <c r="D19" s="10" t="inlineStr"/>
-      <c r="E19" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
@@ -8718,9 +8718,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="N19" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="N19" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="O19" s="8">
@@ -8837,9 +8837,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F20" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="F20" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="G20" s="15" t="inlineStr">
@@ -8877,9 +8877,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="N20" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="N20" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="O20" s="8">
@@ -9051,14 +9051,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S21" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S21" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="T21" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="U21" s="8" t="inlineStr">
@@ -9090,9 +9090,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB21" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AB21" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AC21" s="8" t="inlineStr">
@@ -9105,9 +9105,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AE21" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AE21" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AF21" s="8" t="inlineStr">
@@ -9151,9 +9151,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F22" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="F22" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="G22" s="11" t="inlineStr">
@@ -9161,9 +9161,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="H22" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="H22" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="I22" s="15" t="inlineStr">
@@ -9239,9 +9239,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Z22" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="Z22" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AA22" s="15" t="inlineStr">
@@ -9249,9 +9249,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB22" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AB22" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AC22" s="15" t="inlineStr">
@@ -9316,9 +9316,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H23" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="I23" s="8" t="inlineStr">
@@ -9331,9 +9331,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K23" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="K23" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="L23" s="8" t="inlineStr">
@@ -9761,9 +9761,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H26" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="I26" s="8" t="inlineStr">
@@ -9791,9 +9791,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="N26" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="N26" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="O26" s="8">
@@ -9810,14 +9810,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S26" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T26" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S26" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="U26" s="8" t="inlineStr">
@@ -9849,9 +9849,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB26" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AB26" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AC26" s="8" t="inlineStr">
@@ -9901,14 +9901,14 @@
       </c>
       <c r="C27" s="9" t="inlineStr"/>
       <c r="D27" s="10" t="inlineStr"/>
-      <c r="E27" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="F27" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="G27" s="8" t="inlineStr">
@@ -9965,14 +9965,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S27" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S27" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="T27" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="U27" s="11" t="inlineStr">
@@ -10061,14 +10061,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F28" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="G28" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="F28" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
@@ -10125,14 +10125,14 @@
           <t>公</t>
         </is>
       </c>
-      <c r="T28" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="U28" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="V28" s="8">
@@ -10149,9 +10149,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="Z28" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="Z28" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AA28" s="8" t="inlineStr">
@@ -10164,14 +10164,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC28" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AD28" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AC28" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="AD28" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AE28" s="8" t="inlineStr">
@@ -10221,9 +10221,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="G29" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="G29" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
@@ -10246,9 +10246,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="L29" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="L29" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="M29" s="8" t="inlineStr">
@@ -10275,9 +10275,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="S29" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S29" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="T29" s="8" t="inlineStr">
@@ -10285,9 +10285,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="U29" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="U29" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="V29" s="8">
@@ -10314,24 +10314,24 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB29" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AC29" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AD29" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AE29" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AB29" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="AC29" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AD29" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AE29" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AF29" s="8" t="inlineStr">
@@ -10381,9 +10381,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H30" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="H30" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="I30" s="8" t="inlineStr">
@@ -10411,18 +10411,18 @@
           <t>公</t>
         </is>
       </c>
-      <c r="N30" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="N30" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="O30" s="8">
         <f>COUNTIF(E30:N30, "○")</f>
         <v/>
       </c>
-      <c r="Q30" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Q30" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="R30" s="8" t="inlineStr">
@@ -10435,9 +10435,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="T30" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="U30" s="11" t="inlineStr">
@@ -10484,9 +10484,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AE30" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AE30" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AF30" s="8" t="inlineStr">
@@ -10718,9 +10718,9 @@
         <f>COUNTIF(E32:N32, "○")</f>
         <v/>
       </c>
-      <c r="Q32" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="Q32" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="R32" s="8" t="inlineStr">
@@ -10728,9 +10728,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S32" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S32" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="T32" s="11" t="inlineStr">
@@ -10757,9 +10757,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Z32" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z32" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AA32" s="8" t="inlineStr">
@@ -10772,19 +10772,19 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC32" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AD32" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AE32" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AC32" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AD32" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="AE32" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AF32" s="8" t="inlineStr">
@@ -11492,9 +11492,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H3" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="H3" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="I3" s="8" t="inlineStr">
@@ -11522,9 +11522,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="N3" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="N3" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="O3" s="8">
@@ -11580,9 +11580,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB3" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AB3" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AC3" s="8" t="inlineStr">
@@ -11646,9 +11646,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="G4" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="H4" s="15" t="inlineStr">
@@ -11695,9 +11695,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="R4" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="R4" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="S4" s="15" t="inlineStr">
@@ -11705,9 +11705,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="T4" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="T4" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="U4" s="15" t="inlineStr">
@@ -11855,14 +11855,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S5" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T5" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S5" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="U5" s="8" t="inlineStr">
@@ -11884,9 +11884,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="Z5" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="Z5" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AA5" s="8" t="inlineStr">
@@ -11899,9 +11899,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC5" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AC5" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AD5" s="8" t="inlineStr">
@@ -11909,9 +11909,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AE5" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AE5" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AF5" s="8" t="inlineStr">
@@ -11960,9 +11960,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="G6" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="H6" s="15" t="inlineStr">
@@ -12009,9 +12009,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="R6" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="R6" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="S6" s="15" t="inlineStr">
@@ -12019,9 +12019,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="T6" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="T6" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="U6" s="15" t="inlineStr">
@@ -12053,9 +12053,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB6" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AB6" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AC6" s="15" t="inlineStr">
@@ -12063,9 +12063,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AD6" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AD6" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AE6" s="15" t="inlineStr">
@@ -12120,9 +12120,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H7" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="I7" s="8" t="inlineStr">
@@ -12150,9 +12150,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="N7" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="N7" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="O7" s="8">
@@ -12467,9 +12467,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S9" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S9" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="T9" s="8" t="inlineStr">
@@ -12477,9 +12477,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="U9" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="U9" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="V9" s="8">
@@ -12496,9 +12496,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Z9" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z9" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AA9" s="8" t="inlineStr">
@@ -12511,19 +12511,19 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC9" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AD9" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AE9" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AC9" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AD9" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="AE9" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AF9" s="8" t="inlineStr">
@@ -12573,9 +12573,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="I10" s="8" t="inlineStr">
@@ -12603,9 +12603,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="N10" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="N10" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="O10" s="8">
@@ -12622,9 +12622,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S10" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S10" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="T10" s="8" t="inlineStr">
@@ -12632,9 +12632,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="U10" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="U10" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="V10" s="8">
@@ -12661,9 +12661,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB10" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AB10" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AC10" s="8" t="inlineStr">
@@ -12723,9 +12723,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="G11" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
@@ -12772,9 +12772,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="R11" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="R11" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="S11" s="8" t="inlineStr">
@@ -12932,9 +12932,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S12" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S12" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="T12" s="11" t="inlineStr">
@@ -12961,9 +12961,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="Z12" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="Z12" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AA12" s="8" t="inlineStr">
@@ -12976,9 +12976,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC12" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AC12" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AD12" s="8" t="inlineStr">
@@ -12986,9 +12986,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AE12" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AE12" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AF12" s="8" t="inlineStr">
@@ -13037,9 +13037,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="G13" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="G13" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="H13" s="15" t="inlineStr">
@@ -13086,14 +13086,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="R13" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="S13" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="R13" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="S13" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="T13" s="15" t="inlineStr">
@@ -13130,9 +13130,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB13" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AB13" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AC13" s="15" t="inlineStr">
@@ -13140,9 +13140,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AD13" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AD13" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AE13" s="15" t="inlineStr">
@@ -13197,9 +13197,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H14" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="H14" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="I14" s="8" t="inlineStr">
@@ -13227,9 +13227,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="N14" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="N14" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="O14" s="8">
@@ -13549,9 +13549,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="T16" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="U16" s="8" t="inlineStr">
@@ -13573,9 +13573,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Z16" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z16" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AA16" s="8" t="inlineStr">
@@ -13588,19 +13588,19 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC16" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AD16" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AE16" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AC16" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AD16" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="AE16" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AF16" s="8" t="inlineStr">
@@ -13654,9 +13654,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H17" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="H17" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="I17" s="15" t="inlineStr">
@@ -13684,9 +13684,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="N17" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="N17" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="O17" s="8">
@@ -13742,9 +13742,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB17" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AB17" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AC17" s="15" t="inlineStr">
@@ -13757,9 +13757,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AE17" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AE17" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AF17" s="15" t="inlineStr">
@@ -13804,9 +13804,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="G18" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
@@ -13814,9 +13814,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="I18" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="I18" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="J18" s="8" t="inlineStr">
@@ -13853,24 +13853,24 @@
           <t>○</t>
         </is>
       </c>
-      <c r="R18" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="S18" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T18" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="R18" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="S18" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="U18" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="V18" s="8">
@@ -13969,9 +13969,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="I19" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="I19" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="J19" s="8" t="inlineStr">
@@ -14008,14 +14008,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="R19" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="S19" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="R19" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="S19" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
@@ -14023,9 +14023,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="U19" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="V19" s="8">
@@ -14042,9 +14042,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="Z19" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="Z19" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AA19" s="8" t="inlineStr">
@@ -14057,9 +14057,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC19" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AC19" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AD19" s="8" t="inlineStr">
@@ -14118,9 +14118,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="G20" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="G20" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="H20" s="15" t="inlineStr">
@@ -14211,9 +14211,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB20" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AB20" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AC20" s="15" t="inlineStr">
@@ -14221,9 +14221,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AD20" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AD20" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AE20" s="15" t="inlineStr">
@@ -14278,9 +14278,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H21" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="I21" s="8" t="inlineStr">
@@ -14308,9 +14308,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="N21" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="N21" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="O21" s="8">
@@ -14625,14 +14625,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S23" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S23" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="T23" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="U23" s="8" t="inlineStr">
@@ -14654,9 +14654,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Z23" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z23" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AA23" s="8" t="inlineStr">
@@ -14669,19 +14669,19 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC23" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AD23" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AE23" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AC23" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AD23" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="AE23" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AF23" s="8" t="inlineStr">
@@ -14731,9 +14731,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H24" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="I24" s="8" t="inlineStr">
@@ -14761,9 +14761,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="N24" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="N24" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="O24" s="8">
@@ -14819,9 +14819,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB24" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AB24" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AC24" s="8" t="inlineStr">
@@ -14834,9 +14834,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AE24" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AE24" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AF24" s="8" t="inlineStr">
@@ -14881,9 +14881,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="G25" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
@@ -14891,9 +14891,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="I25" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="I25" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="J25" s="8" t="inlineStr">
@@ -14935,9 +14935,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="S25" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S25" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="T25" s="8" t="inlineStr">
@@ -14945,9 +14945,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="U25" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="V25" s="8">
@@ -15046,9 +15046,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="I26" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="I26" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="J26" s="8" t="inlineStr">
@@ -15090,14 +15090,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S26" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T26" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S26" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="U26" s="8" t="inlineStr">
@@ -15119,9 +15119,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="Z26" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="Z26" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AA26" s="8" t="inlineStr">
@@ -15134,9 +15134,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC26" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AC26" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AD26" s="8" t="inlineStr">
@@ -15191,9 +15191,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="G27" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="G27" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
@@ -15250,14 +15250,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="U27" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="T27" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="V27" s="8">
@@ -15284,9 +15284,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB27" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AB27" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AC27" s="8" t="inlineStr">
@@ -15294,9 +15294,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AD27" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AD27" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AE27" s="8" t="inlineStr">
@@ -15351,9 +15351,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H28" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="H28" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="I28" s="8" t="inlineStr">
@@ -15381,9 +15381,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="N28" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="N28" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="O28" s="8">
@@ -15727,9 +15727,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Z30" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z30" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AA30" s="8" t="inlineStr">
@@ -15742,19 +15742,19 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC30" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AD30" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AE30" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AC30" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AD30" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="AE30" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AF30" s="8" t="inlineStr">
@@ -15788,11 +15788,7 @@
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr"/>
-      <c r="D31" s="12" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+      <c r="D31" s="10" t="inlineStr"/>
       <c r="E31" s="8" t="inlineStr">
         <is>
           <t>特有</t>
@@ -15947,11 +15943,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr"/>
-      <c r="D32" s="12" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+      <c r="D32" s="10" t="inlineStr"/>
       <c r="E32" s="8" t="inlineStr">
         <is>
           <t>特有</t>
@@ -16106,11 +16098,7 @@
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr"/>
-      <c r="D33" s="12" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+      <c r="D33" s="10" t="inlineStr"/>
       <c r="E33" s="8" t="inlineStr">
         <is>
           <t>特有</t>

--- a/26年10-12月シフト.xlsx
+++ b/26年10-12月シフト.xlsx
@@ -732,42 +732,42 @@
       </c>
       <c r="Z2" s="7" t="inlineStr">
         <is>
+          <t>岡本</t>
+        </is>
+      </c>
+      <c r="AA2" s="7" t="inlineStr">
+        <is>
           <t>石渡</t>
         </is>
       </c>
-      <c r="AA2" s="7" t="inlineStr">
+      <c r="AB2" s="7" t="inlineStr">
         <is>
           <t>今川</t>
         </is>
       </c>
-      <c r="AB2" s="7" t="inlineStr">
+      <c r="AC2" s="7" t="inlineStr">
         <is>
           <t>野田</t>
         </is>
       </c>
-      <c r="AC2" s="7" t="inlineStr">
+      <c r="AD2" s="7" t="inlineStr">
         <is>
           <t>岸</t>
         </is>
       </c>
-      <c r="AD2" s="7" t="inlineStr">
+      <c r="AE2" s="7" t="inlineStr">
         <is>
           <t>鹿島</t>
         </is>
       </c>
-      <c r="AE2" s="7" t="inlineStr">
+      <c r="AF2" s="7" t="inlineStr">
         <is>
           <t>分部</t>
         </is>
       </c>
-      <c r="AF2" s="7" t="inlineStr">
+      <c r="AG2" s="7" t="inlineStr">
         <is>
           <t>太田</t>
-        </is>
-      </c>
-      <c r="AG2" s="7" t="inlineStr">
-        <is>
-          <t>岡本</t>
         </is>
       </c>
       <c r="AH2" s="5" t="inlineStr">
@@ -814,9 +814,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="I3" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="J3" s="8" t="inlineStr">
@@ -863,9 +863,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="T3" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="U3" s="8" t="inlineStr">
@@ -907,24 +907,24 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AD3" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AE3" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AF3" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AG3" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AD3" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="AE3" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AF3" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AG3" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AH3" s="8">
@@ -954,19 +954,19 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="H4" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="F4" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="G4" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="I4" s="8" t="inlineStr">
@@ -979,14 +979,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K4" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="L4" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="K4" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="L4" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="M4" s="8" t="inlineStr">
@@ -1008,9 +1008,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="R4" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="R4" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="S4" s="8" t="inlineStr">
@@ -1018,14 +1018,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="U4" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="T4" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="V4" s="8">
@@ -1042,9 +1042,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Z4" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="Z4" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AA4" s="8" t="inlineStr">
@@ -1067,14 +1067,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AE4" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AF4" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AE4" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="AF4" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AG4" s="8" t="inlineStr">
@@ -1119,9 +1119,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H5" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="I5" s="8" t="inlineStr">
@@ -1129,9 +1129,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="J5" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="J5" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="K5" s="8" t="inlineStr">
@@ -1168,9 +1168,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S5" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S5" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="T5" s="8" t="inlineStr">
@@ -1197,19 +1197,19 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Z5" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AA5" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AB5" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z5" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="AA5" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AB5" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AC5" s="8" t="inlineStr">
@@ -1232,9 +1232,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AG5" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AG5" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AH5" s="8">
@@ -1411,9 +1411,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F7" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
@@ -1441,9 +1441,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="L7" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="L7" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="M7" s="8" t="inlineStr">
@@ -1465,9 +1465,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="R7" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="R7" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="S7" s="11" t="inlineStr">
@@ -1504,9 +1504,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AA7" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AA7" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AB7" s="8" t="inlineStr">
@@ -1519,14 +1519,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AD7" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AE7" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AD7" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AE7" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AF7" s="8" t="inlineStr">
@@ -1581,9 +1581,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="I8" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="J8" s="8" t="inlineStr">
@@ -1606,9 +1606,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="N8" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="N8" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="O8" s="8">
@@ -1630,14 +1630,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="T8" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="U8" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="V8" s="8">
@@ -1654,9 +1654,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="Z8" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z8" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AA8" s="8" t="inlineStr">
@@ -1664,9 +1664,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB8" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AB8" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AC8" s="8" t="inlineStr">
@@ -1689,9 +1689,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AG8" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AG8" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AH8" s="8">
@@ -1726,14 +1726,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="G9" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="H9" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H9" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="I9" s="8" t="inlineStr">
@@ -1746,9 +1746,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K9" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="K9" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="L9" s="8" t="inlineStr">
@@ -1761,9 +1761,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="N9" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="N9" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="O9" s="8">
@@ -1780,14 +1780,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S9" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S9" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="T9" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="U9" s="8" t="inlineStr">
@@ -1809,9 +1809,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="Z9" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z9" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AA9" s="8" t="inlineStr">
@@ -1844,9 +1844,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AG9" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AG9" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AH9" s="8">
@@ -1891,9 +1891,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="I10" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="I10" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="J10" s="8" t="inlineStr">
@@ -1906,9 +1906,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="L10" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="L10" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="M10" s="8" t="inlineStr">
@@ -1935,9 +1935,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S10" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S10" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="T10" s="8" t="inlineStr">
@@ -1945,9 +1945,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="U10" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="U10" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="V10" s="8">
@@ -1984,9 +1984,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AD10" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AD10" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AE10" s="8" t="inlineStr">
@@ -1994,14 +1994,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AF10" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AG10" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AF10" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AG10" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AH10" s="8">
@@ -2035,19 +2035,19 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F11" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="G11" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="H11" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="G11" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="H11" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="I11" s="15" t="inlineStr">
@@ -2060,9 +2060,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K11" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="K11" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="L11" s="15" t="inlineStr">
@@ -2089,9 +2089,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="R11" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="R11" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="S11" s="15" t="inlineStr">
@@ -2123,9 +2123,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Z11" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="Z11" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AA11" s="15" t="inlineStr">
@@ -2133,9 +2133,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB11" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AB11" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AC11" s="15" t="inlineStr">
@@ -2148,14 +2148,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AE11" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AF11" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AE11" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="AF11" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AG11" s="15" t="inlineStr">
@@ -2254,9 +2254,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="T12" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="U12" s="11" t="inlineStr">
@@ -2278,19 +2278,19 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Z12" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AA12" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AB12" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z12" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="AA12" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AB12" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AC12" s="8" t="inlineStr">
@@ -2313,9 +2313,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AG12" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AG12" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AH12" s="8">
@@ -2635,9 +2635,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F15" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="G15" s="8" t="inlineStr">
@@ -2675,9 +2675,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="N15" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="N15" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="O15" s="8">
@@ -2694,9 +2694,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S15" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S15" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="T15" s="8" t="inlineStr">
@@ -2704,9 +2704,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="U15" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="V15" s="8">
@@ -2723,14 +2723,14 @@
           <t>公</t>
         </is>
       </c>
-      <c r="Z15" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AA15" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z15" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="AA15" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AB15" s="8" t="inlineStr">
@@ -2738,9 +2738,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC15" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AC15" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AD15" s="8" t="inlineStr">
@@ -2758,9 +2758,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AG15" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AG15" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AH15" s="8">
@@ -2794,19 +2794,19 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F16" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="G16" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="H16" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="F16" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="G16" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H16" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="I16" s="15" t="inlineStr">
@@ -2819,9 +2819,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K16" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="K16" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="L16" s="15" t="inlineStr">
@@ -2848,9 +2848,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="R16" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="R16" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="S16" s="15" t="inlineStr">
@@ -2858,9 +2858,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="T16" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="T16" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="U16" s="15" t="inlineStr">
@@ -2882,9 +2882,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="Z16" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z16" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AA16" s="15" t="inlineStr">
@@ -2897,9 +2897,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC16" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AC16" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AD16" s="15" t="inlineStr">
@@ -2907,9 +2907,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AE16" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AE16" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AF16" s="15" t="inlineStr">
@@ -2917,9 +2917,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AG16" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AG16" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AH16" s="8">
@@ -2964,9 +2964,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="I17" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="I17" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="J17" s="8" t="inlineStr">
@@ -2979,9 +2979,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="L17" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="L17" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="M17" s="8" t="inlineStr">
@@ -3008,19 +3008,19 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S17" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T17" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="U17" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S17" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="V17" s="8">
@@ -3052,14 +3052,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC17" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AD17" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AC17" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AD17" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AE17" s="8" t="inlineStr">
@@ -3067,14 +3067,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AF17" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AG17" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AF17" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AG17" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AH17" s="8">
@@ -3108,19 +3108,19 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F18" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="G18" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="H18" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="H18" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="I18" s="15" t="inlineStr">
@@ -3133,9 +3133,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K18" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="K18" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="L18" s="15" t="inlineStr">
@@ -3162,9 +3162,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="R18" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="R18" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="S18" s="15" t="inlineStr">
@@ -3196,9 +3196,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Z18" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="Z18" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AA18" s="15" t="inlineStr">
@@ -3216,19 +3216,19 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AD18" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AE18" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AF18" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AD18" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AE18" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="AF18" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AG18" s="15" t="inlineStr">
@@ -3278,14 +3278,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="I19" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="J19" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="I19" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="J19" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="K19" s="8" t="inlineStr">
@@ -3351,19 +3351,19 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Z19" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AA19" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AB19" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z19" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="AA19" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AB19" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AC19" s="8" t="inlineStr">
@@ -3386,9 +3386,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AG19" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AG19" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AH19" s="8">
@@ -3591,9 +3591,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="L21" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="L21" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="M21" s="8" t="inlineStr">
@@ -3601,9 +3601,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="N21" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="N21" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="O21" s="8">
@@ -3615,19 +3615,19 @@
           <t>○</t>
         </is>
       </c>
-      <c r="R21" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="S21" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T21" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="R21" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="S21" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="U21" s="8" t="inlineStr">
@@ -3649,19 +3649,19 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Z21" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AA21" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AB21" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="Z21" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AA21" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="AB21" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AC21" s="8" t="inlineStr">
@@ -3721,9 +3721,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="G22" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
@@ -3756,9 +3756,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="N22" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="N22" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="O22" s="8">
@@ -3775,9 +3775,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S22" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S22" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="T22" s="8" t="inlineStr">
@@ -3785,9 +3785,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="U22" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="V22" s="8">
@@ -3804,9 +3804,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="Z22" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z22" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AA22" s="8" t="inlineStr">
@@ -3829,9 +3829,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AE22" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AE22" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AF22" s="8" t="inlineStr">
@@ -3839,9 +3839,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AG22" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AG22" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AH22" s="8">
@@ -3866,14 +3866,14 @@
       </c>
       <c r="C23" s="9" t="inlineStr"/>
       <c r="D23" s="10" t="inlineStr"/>
-      <c r="E23" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="F23" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="G23" s="8" t="inlineStr">
@@ -3881,9 +3881,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H23" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="H23" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="I23" s="8" t="inlineStr">
@@ -3896,9 +3896,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K23" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="K23" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="L23" s="8" t="inlineStr">
@@ -3930,14 +3930,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S23" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S23" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="T23" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="U23" s="8" t="inlineStr">
@@ -3959,9 +3959,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="Z23" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z23" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AA23" s="8" t="inlineStr">
@@ -3994,9 +3994,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AG23" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AG23" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AH23" s="8">
@@ -4021,9 +4021,9 @@
       </c>
       <c r="C24" s="9" t="inlineStr"/>
       <c r="D24" s="10" t="inlineStr"/>
-      <c r="E24" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
@@ -4036,14 +4036,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H24" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="I24" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="I24" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="J24" s="8" t="inlineStr">
@@ -4056,9 +4056,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="L24" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="L24" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="M24" s="8" t="inlineStr">
@@ -4075,9 +4075,9 @@
         <f>COUNTIF(E24:N24, "○")</f>
         <v/>
       </c>
-      <c r="Q24" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="Q24" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="R24" s="8" t="inlineStr">
@@ -4085,14 +4085,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S24" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T24" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S24" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="U24" s="8" t="inlineStr">
@@ -4134,9 +4134,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AD24" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AD24" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AE24" s="8" t="inlineStr">
@@ -4144,14 +4144,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AF24" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AG24" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AF24" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AG24" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AH24" s="8">
@@ -4185,14 +4185,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F25" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="G25" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="F25" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="G25" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="H25" s="15" t="inlineStr">
@@ -4210,14 +4210,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K25" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="L25" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="K25" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="L25" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="M25" s="15" t="inlineStr">
@@ -4239,19 +4239,19 @@
           <t>○</t>
         </is>
       </c>
-      <c r="R25" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="S25" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="T25" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="R25" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="S25" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="T25" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="U25" s="15" t="inlineStr">
@@ -4293,19 +4293,19 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AD25" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AE25" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AF25" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AD25" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AE25" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="AF25" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AG25" s="15" t="inlineStr">
@@ -4355,14 +4355,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="I26" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="J26" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="I26" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="J26" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="K26" s="8" t="inlineStr">
@@ -4399,9 +4399,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S26" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S26" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="T26" s="8" t="inlineStr">
@@ -4428,19 +4428,19 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Z26" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AA26" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AB26" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z26" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="AA26" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AB26" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AC26" s="8" t="inlineStr">
@@ -4463,9 +4463,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AG26" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AG26" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AH26" s="8">
@@ -4668,9 +4668,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="L28" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="L28" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="M28" s="8" t="inlineStr">
@@ -4678,9 +4678,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="N28" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="N28" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="O28" s="8">
@@ -4692,14 +4692,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="R28" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="S28" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="R28" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="S28" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="T28" s="8" t="inlineStr">
@@ -4707,9 +4707,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="U28" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="V28" s="8">
@@ -4726,24 +4726,24 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Z28" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AA28" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AB28" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AC28" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z28" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AA28" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="AB28" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AC28" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AD28" s="8" t="inlineStr">
@@ -4802,9 +4802,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="G29" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="G29" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="H29" s="15" t="inlineStr">
@@ -4837,9 +4837,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="N29" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="N29" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="O29" s="8">
@@ -4861,9 +4861,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="T29" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="T29" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="U29" s="15" t="inlineStr">
@@ -4885,14 +4885,14 @@
           <t>公</t>
         </is>
       </c>
-      <c r="Z29" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AA29" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z29" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="AA29" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AB29" s="15" t="inlineStr">
@@ -4910,9 +4910,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AE29" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AE29" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AF29" s="15" t="inlineStr">
@@ -4920,9 +4920,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AG29" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AG29" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AH29" s="8">
@@ -4947,14 +4947,14 @@
       </c>
       <c r="C30" s="9" t="inlineStr"/>
       <c r="D30" s="10" t="inlineStr"/>
-      <c r="E30" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="F30" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="G30" s="8" t="inlineStr">
@@ -4962,9 +4962,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H30" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="H30" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="I30" s="8" t="inlineStr">
@@ -4977,9 +4977,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K30" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="K30" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="L30" s="8" t="inlineStr">
@@ -5001,9 +5001,9 @@
         <f>COUNTIF(E30:N30, "○")</f>
         <v/>
       </c>
-      <c r="Q30" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Q30" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="R30" s="8" t="inlineStr">
@@ -5011,19 +5011,19 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S30" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="U30" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S30" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="T30" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="U30" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="V30" s="8">
@@ -5040,9 +5040,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="Z30" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z30" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AA30" s="8" t="inlineStr">
@@ -5075,9 +5075,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AG30" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AG30" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AH30" s="8">
@@ -5102,9 +5102,9 @@
       </c>
       <c r="C31" s="9" t="inlineStr"/>
       <c r="D31" s="10" t="inlineStr"/>
-      <c r="E31" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="F31" s="8" t="inlineStr">
@@ -5117,9 +5117,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H31" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="H31" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="I31" s="11" t="inlineStr">
@@ -5137,9 +5137,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="L31" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="L31" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="M31" s="8" t="inlineStr">
@@ -5166,14 +5166,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S31" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T31" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S31" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="U31" s="11" t="inlineStr">
@@ -5225,14 +5225,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AF31" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AG31" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AF31" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AG31" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AH31" s="8">
@@ -5262,9 +5262,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F32" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="F32" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="G32" s="11" t="inlineStr">
@@ -5287,14 +5287,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K32" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="L32" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="K32" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="L32" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="M32" s="8" t="inlineStr">
@@ -5302,9 +5302,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="N32" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="N32" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="O32" s="8">
@@ -5316,14 +5316,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="R32" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="S32" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="R32" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="S32" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="T32" s="11" t="inlineStr">
@@ -5360,9 +5360,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB32" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AB32" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AC32" s="8" t="inlineStr">
@@ -5370,19 +5370,19 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AD32" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AE32" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AF32" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AD32" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AE32" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="AF32" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AG32" s="8" t="inlineStr">
@@ -5432,19 +5432,19 @@
           <t>○</t>
         </is>
       </c>
-      <c r="I33" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="J33" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="K33" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="I33" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="J33" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="K33" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="L33" s="8" t="inlineStr">
@@ -5471,14 +5471,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="R33" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="S33" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="R33" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="S33" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="T33" s="8" t="inlineStr">
@@ -5505,19 +5505,19 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Z33" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AA33" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AB33" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z33" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="AA33" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AB33" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AC33" s="8" t="inlineStr">
@@ -5540,9 +5540,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AG33" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AG33" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AH33" s="8">
@@ -5719,7 +5719,7 @@
         <v>13</v>
       </c>
       <c r="Z35" s="17" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AA35" s="17" t="n">
         <v>21</v>
@@ -5740,7 +5740,7 @@
         <v>21</v>
       </c>
       <c r="AG35" s="17" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="36" ht="24" customHeight="1">
@@ -5858,127 +5858,127 @@
       </c>
       <c r="E37" s="17" t="inlineStr">
         <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="F37" s="17" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="G37" s="17" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="H37" s="17" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="I37" s="17" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="J37" s="17" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="K37" s="17" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="L37" s="17" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="M37" s="17" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="N37" s="17" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="Q37" s="17" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="R37" s="17" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="S37" s="17" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="T37" s="17" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="U37" s="17" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="X37" s="17" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F37" s="17" t="inlineStr">
+      <c r="Y37" s="17" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G37" s="17" t="inlineStr">
+      <c r="Z37" s="17" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H37" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I37" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J37" s="17" t="inlineStr">
+      <c r="AA37" s="17" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="K37" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L37" s="17" t="inlineStr">
-        <is>
-          <t>火</t>
-        </is>
-      </c>
-      <c r="M37" s="17" t="inlineStr">
+      <c r="AB37" s="17" t="inlineStr">
         <is>
           <t>土</t>
         </is>
       </c>
-      <c r="N37" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q37" s="17" t="inlineStr">
-        <is>
-          <t>火</t>
-        </is>
-      </c>
-      <c r="R37" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S37" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T37" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U37" s="17" t="inlineStr">
-        <is>
-          <t>土</t>
-        </is>
-      </c>
-      <c r="X37" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y37" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z37" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA37" s="17" t="inlineStr">
-        <is>
-          <t>土</t>
-        </is>
-      </c>
-      <c r="AB37" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="AC37" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>水</t>
         </is>
       </c>
       <c r="AD37" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>木</t>
         </is>
       </c>
       <c r="AE37" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>金</t>
         </is>
       </c>
       <c r="AF37" s="17" t="inlineStr">
         <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="AG37" s="17" t="inlineStr">
+        <is>
           <t>木</t>
-        </is>
-      </c>
-      <c r="AG37" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
         </is>
       </c>
     </row>
@@ -6163,42 +6163,42 @@
       </c>
       <c r="Z2" s="7" t="inlineStr">
         <is>
+          <t>岡本</t>
+        </is>
+      </c>
+      <c r="AA2" s="7" t="inlineStr">
+        <is>
           <t>石渡</t>
         </is>
       </c>
-      <c r="AA2" s="7" t="inlineStr">
+      <c r="AB2" s="7" t="inlineStr">
         <is>
           <t>今川</t>
         </is>
       </c>
-      <c r="AB2" s="7" t="inlineStr">
+      <c r="AC2" s="7" t="inlineStr">
         <is>
           <t>野田</t>
         </is>
       </c>
-      <c r="AC2" s="7" t="inlineStr">
+      <c r="AD2" s="7" t="inlineStr">
         <is>
           <t>岸</t>
         </is>
       </c>
-      <c r="AD2" s="7" t="inlineStr">
+      <c r="AE2" s="7" t="inlineStr">
         <is>
           <t>鹿島</t>
         </is>
       </c>
-      <c r="AE2" s="7" t="inlineStr">
+      <c r="AF2" s="7" t="inlineStr">
         <is>
           <t>分部</t>
         </is>
       </c>
-      <c r="AF2" s="7" t="inlineStr">
+      <c r="AG2" s="7" t="inlineStr">
         <is>
           <t>太田</t>
-        </is>
-      </c>
-      <c r="AG2" s="7" t="inlineStr">
-        <is>
-          <t>岡本</t>
         </is>
       </c>
       <c r="AH2" s="5" t="inlineStr">
@@ -6461,14 +6461,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Z4" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AA4" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z4" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AA4" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AB4" s="8" t="inlineStr">
@@ -6476,9 +6476,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC4" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AC4" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AD4" s="8" t="inlineStr">
@@ -6684,9 +6684,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="G6" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="H6" s="15" t="inlineStr">
@@ -6719,18 +6719,18 @@
           <t>○</t>
         </is>
       </c>
-      <c r="N6" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="N6" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="O6" s="8">
         <f>COUNTIF(E6:N6, "○")</f>
         <v/>
       </c>
-      <c r="Q6" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Q6" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="R6" s="15" t="inlineStr">
@@ -6738,9 +6738,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S6" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S6" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="T6" s="15" t="inlineStr">
@@ -6767,9 +6767,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="Z6" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z6" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AA6" s="15" t="inlineStr">
@@ -6797,9 +6797,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AF6" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AF6" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AG6" s="11" t="inlineStr">
@@ -6829,9 +6829,9 @@
       </c>
       <c r="C7" s="9" t="inlineStr"/>
       <c r="D7" s="10" t="inlineStr"/>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
@@ -6844,14 +6844,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H7" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="I7" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="J7" s="8" t="inlineStr">
@@ -6864,9 +6864,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="L7" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="L7" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="M7" s="8" t="inlineStr">
@@ -6888,14 +6888,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="R7" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="S7" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="R7" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="S7" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="T7" s="8" t="inlineStr">
@@ -6903,9 +6903,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="U7" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="V7" s="8">
@@ -6952,9 +6952,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="AF7" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AF7" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AG7" s="8" t="inlineStr">
@@ -6998,14 +6998,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="G8" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="H8" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="G8" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H8" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="I8" s="15" t="inlineStr">
@@ -7018,9 +7018,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K8" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="K8" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="L8" s="15" t="inlineStr">
@@ -7033,9 +7033,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="N8" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="N8" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="O8" s="8">
@@ -7047,14 +7047,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="R8" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="S8" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="R8" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="S8" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="T8" s="15" t="inlineStr">
@@ -7091,19 +7091,19 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB8" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AC8" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AD8" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AB8" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AC8" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="AD8" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AE8" s="15" t="inlineStr">
@@ -7163,9 +7163,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="I9" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="I9" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="J9" s="8" t="inlineStr">
@@ -7173,9 +7173,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K9" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="K9" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="L9" s="8" t="inlineStr">
@@ -7236,19 +7236,19 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Z9" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AA9" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AB9" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z9" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="AA9" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AB9" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AC9" s="8" t="inlineStr">
@@ -7271,9 +7271,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AG9" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AG9" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AH9" s="8">
@@ -7441,9 +7441,9 @@
       </c>
       <c r="C11" s="9" t="inlineStr"/>
       <c r="D11" s="10" t="inlineStr"/>
-      <c r="E11" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
@@ -7476,9 +7476,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="L11" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="L11" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="M11" s="8" t="inlineStr">
@@ -7497,7 +7497,7 @@
       </c>
       <c r="Q11" s="8" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>特有</t>
         </is>
       </c>
       <c r="R11" s="8" t="inlineStr">
@@ -7515,9 +7515,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="U11" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="U11" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="V11" s="8">
@@ -7534,9 +7534,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Z11" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="Z11" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AA11" s="8" t="inlineStr">
@@ -7554,9 +7554,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AD11" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AD11" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AE11" s="8" t="inlineStr">
@@ -7616,9 +7616,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="I12" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="I12" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="J12" s="8" t="inlineStr">
@@ -7638,21 +7638,21 @@
       </c>
       <c r="M12" s="8" t="inlineStr">
         <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="N12" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+          <t>有休</t>
+        </is>
+      </c>
+      <c r="N12" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="O12" s="8">
         <f>COUNTIF(E12:N12, "○")</f>
         <v/>
       </c>
-      <c r="Q12" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="Q12" s="8" t="inlineStr">
+        <is>
+          <t>特有</t>
         </is>
       </c>
       <c r="R12" s="8" t="inlineStr">
@@ -7689,14 +7689,14 @@
           <t>公</t>
         </is>
       </c>
-      <c r="Z12" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AA12" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z12" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="AA12" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AB12" s="8" t="inlineStr">
@@ -7704,9 +7704,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC12" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AC12" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AD12" s="8" t="inlineStr">
@@ -7724,9 +7724,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AG12" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AG12" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AH12" s="8">
@@ -7761,9 +7761,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="G13" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
@@ -7820,14 +7820,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="U13" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="T13" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="V13" s="8">
@@ -7844,9 +7844,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="Z13" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z13" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AA13" s="8" t="inlineStr">
@@ -7874,9 +7874,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AF13" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AF13" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AG13" s="11" t="inlineStr">
@@ -7906,9 +7906,9 @@
       </c>
       <c r="C14" s="9" t="inlineStr"/>
       <c r="D14" s="10" t="inlineStr"/>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
@@ -7921,14 +7921,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H14" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="I14" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="H14" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="J14" s="8" t="inlineStr">
@@ -7941,9 +7941,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="L14" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="L14" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="M14" s="8" t="inlineStr">
@@ -7965,9 +7965,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="R14" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="R14" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="S14" s="8" t="inlineStr">
@@ -7975,14 +7975,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="T14" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="U14" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="V14" s="8">
@@ -8029,9 +8029,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="AF14" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AF14" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AG14" s="8" t="inlineStr">
@@ -8075,14 +8075,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="G15" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="H15" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="G15" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H15" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="I15" s="15" t="inlineStr">
@@ -8095,9 +8095,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K15" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="K15" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="L15" s="15" t="inlineStr">
@@ -8110,9 +8110,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="N15" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="N15" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="O15" s="8">
@@ -8124,14 +8124,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="R15" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="S15" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="R15" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="S15" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="T15" s="15" t="inlineStr">
@@ -8168,19 +8168,19 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB15" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AC15" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AD15" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AB15" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AC15" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="AD15" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AE15" s="15" t="inlineStr">
@@ -8250,9 +8250,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K16" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="K16" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="L16" s="8" t="inlineStr">
@@ -8284,9 +8284,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S16" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S16" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="T16" s="8" t="inlineStr">
@@ -8313,19 +8313,19 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Z16" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AA16" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AB16" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z16" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="AA16" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AB16" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AC16" s="8" t="inlineStr">
@@ -8348,9 +8348,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AG16" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AG16" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AH16" s="8">
@@ -8518,9 +8518,9 @@
       </c>
       <c r="C18" s="9" t="inlineStr"/>
       <c r="D18" s="10" t="inlineStr"/>
-      <c r="E18" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
@@ -8553,9 +8553,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="L18" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="L18" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="M18" s="8" t="inlineStr">
@@ -8577,19 +8577,19 @@
           <t>○</t>
         </is>
       </c>
-      <c r="R18" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="S18" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="R18" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="S18" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="T18" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="U18" s="8" t="inlineStr">
@@ -8611,9 +8611,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Z18" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="Z18" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AA18" s="8" t="inlineStr">
@@ -8631,9 +8631,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AD18" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AD18" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AE18" s="8" t="inlineStr">
@@ -8693,9 +8693,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="I19" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="I19" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="J19" s="8" t="inlineStr">
@@ -8718,9 +8718,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="N19" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="N19" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="O19" s="8">
@@ -8734,7 +8734,7 @@
       </c>
       <c r="R19" s="8" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>特有</t>
         </is>
       </c>
       <c r="S19" s="8" t="inlineStr">
@@ -8742,9 +8742,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="T19" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="U19" s="8" t="inlineStr">
@@ -8766,14 +8766,14 @@
           <t>公</t>
         </is>
       </c>
-      <c r="Z19" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AA19" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z19" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="AA19" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AB19" s="8" t="inlineStr">
@@ -8781,9 +8781,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC19" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AC19" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AD19" s="8" t="inlineStr">
@@ -8801,9 +8801,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AG19" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AG19" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AH19" s="8">
@@ -8842,9 +8842,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="G20" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="G20" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="H20" s="15" t="inlineStr">
@@ -8891,9 +8891,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="R20" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="R20" s="8" t="inlineStr">
+        <is>
+          <t>特有</t>
         </is>
       </c>
       <c r="S20" s="15" t="inlineStr">
@@ -8901,9 +8901,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="T20" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="T20" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="U20" s="15" t="inlineStr">
@@ -8925,9 +8925,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="Z20" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z20" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AA20" s="15" t="inlineStr">
@@ -8955,9 +8955,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AF20" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AF20" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AG20" s="11" t="inlineStr">
@@ -8987,9 +8987,9 @@
       </c>
       <c r="C21" s="9" t="inlineStr"/>
       <c r="D21" s="10" t="inlineStr"/>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="F21" s="8" t="inlineStr">
@@ -9002,14 +9002,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H21" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="I21" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="I21" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="J21" s="8" t="inlineStr">
@@ -9022,9 +9022,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="L21" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="L21" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="M21" s="8" t="inlineStr">
@@ -9048,7 +9048,7 @@
       </c>
       <c r="R21" s="8" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>特有</t>
         </is>
       </c>
       <c r="S21" s="8" t="inlineStr">
@@ -9056,14 +9056,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="T21" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="U21" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="V21" s="8">
@@ -9110,9 +9110,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="AF21" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AF21" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AG21" s="8" t="inlineStr">
@@ -9156,14 +9156,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="G22" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="H22" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="G22" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H22" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="I22" s="15" t="inlineStr">
@@ -9176,9 +9176,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K22" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="K22" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="L22" s="15" t="inlineStr">
@@ -9191,9 +9191,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="N22" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="N22" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="O22" s="8">
@@ -9205,19 +9205,19 @@
           <t>○</t>
         </is>
       </c>
-      <c r="R22" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="S22" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T22" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="R22" s="8" t="inlineStr">
+        <is>
+          <t>特有</t>
+        </is>
+      </c>
+      <c r="S22" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="T22" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="U22" s="15" t="inlineStr">
@@ -9249,19 +9249,19 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB22" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AC22" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AD22" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AB22" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AC22" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="AD22" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AE22" s="15" t="inlineStr">
@@ -9331,9 +9331,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K23" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="K23" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="L23" s="8" t="inlineStr">
@@ -9362,7 +9362,7 @@
       </c>
       <c r="R23" s="8" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>特有</t>
         </is>
       </c>
       <c r="S23" s="8" t="inlineStr">
@@ -9394,19 +9394,19 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Z23" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AA23" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AB23" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z23" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="AA23" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AB23" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AC23" s="8" t="inlineStr">
@@ -9429,9 +9429,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AG23" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AG23" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AH23" s="8">
@@ -9766,9 +9766,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="I26" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="I26" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="J26" s="8" t="inlineStr">
@@ -9791,9 +9791,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="N26" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="N26" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="O26" s="8">
@@ -9810,14 +9810,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S26" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S26" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="T26" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="U26" s="8" t="inlineStr">
@@ -9839,14 +9839,14 @@
           <t>公</t>
         </is>
       </c>
-      <c r="Z26" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AA26" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z26" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="AA26" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AB26" s="8" t="inlineStr">
@@ -9874,9 +9874,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AG26" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AG26" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AH26" s="8">
@@ -9901,19 +9901,19 @@
       </c>
       <c r="C27" s="9" t="inlineStr"/>
       <c r="D27" s="10" t="inlineStr"/>
-      <c r="E27" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="F27" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="G27" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F27" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="G27" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
@@ -9921,9 +9921,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="I27" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="I27" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="J27" s="8" t="inlineStr">
@@ -9965,19 +9965,19 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S27" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T27" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="U27" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S27" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="V27" s="8">
@@ -9994,9 +9994,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="Z27" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z27" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AA27" s="8" t="inlineStr">
@@ -10024,9 +10024,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AF27" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AF27" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AG27" s="11" t="inlineStr">
@@ -10056,14 +10056,14 @@
       </c>
       <c r="C28" s="9" t="inlineStr"/>
       <c r="D28" s="10" t="inlineStr"/>
-      <c r="E28" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="F28" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="G28" s="8" t="inlineStr">
@@ -10071,9 +10071,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H28" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="H28" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="I28" s="8" t="inlineStr">
@@ -10091,9 +10091,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="L28" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="L28" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="M28" s="8" t="inlineStr">
@@ -10115,24 +10115,24 @@
           <t>○</t>
         </is>
       </c>
-      <c r="R28" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="S28" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="U28" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="R28" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="S28" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="T28" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="V28" s="8">
@@ -10164,24 +10164,24 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC28" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AD28" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AE28" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AF28" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AC28" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AD28" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AE28" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="AF28" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AG28" s="8" t="inlineStr">
@@ -10221,9 +10221,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="G29" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
@@ -10246,9 +10246,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="L29" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="L29" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="M29" s="8" t="inlineStr">
@@ -10256,9 +10256,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="N29" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="N29" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="O29" s="8">
@@ -10270,9 +10270,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="R29" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="R29" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="S29" s="11" t="inlineStr">
@@ -10285,9 +10285,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="U29" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="V29" s="8">
@@ -10314,24 +10314,24 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB29" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AC29" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AD29" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AE29" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AB29" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AC29" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="AD29" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="AE29" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AF29" s="8" t="inlineStr">
@@ -10381,9 +10381,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H30" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="H30" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="I30" s="8" t="inlineStr">
@@ -10420,9 +10420,9 @@
         <f>COUNTIF(E30:N30, "○")</f>
         <v/>
       </c>
-      <c r="Q30" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="Q30" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="R30" s="8" t="inlineStr">
@@ -10430,9 +10430,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S30" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S30" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="T30" s="8" t="inlineStr">
@@ -10459,19 +10459,19 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Z30" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AA30" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AB30" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z30" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="AA30" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AB30" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AC30" s="8" t="inlineStr">
@@ -10494,9 +10494,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AG30" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AG30" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AH30" s="8">
@@ -10664,9 +10664,9 @@
       </c>
       <c r="C32" s="9" t="inlineStr"/>
       <c r="D32" s="10" t="inlineStr"/>
-      <c r="E32" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
@@ -10699,9 +10699,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="L32" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="L32" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="M32" s="8" t="inlineStr">
@@ -10718,9 +10718,9 @@
         <f>COUNTIF(E32:N32, "○")</f>
         <v/>
       </c>
-      <c r="Q32" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Q32" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="R32" s="8" t="inlineStr">
@@ -10728,9 +10728,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S32" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S32" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="T32" s="11" t="inlineStr">
@@ -10757,9 +10757,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Z32" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="Z32" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AA32" s="8" t="inlineStr">
@@ -10777,9 +10777,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AD32" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AD32" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AE32" s="8" t="inlineStr">
@@ -10944,16 +10944,16 @@
         <v>15</v>
       </c>
       <c r="M34" s="17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N34" s="17" t="n">
         <v>19</v>
       </c>
       <c r="Q34" s="17" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="R34" s="17" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="S34" s="17" t="n">
         <v>15</v>
@@ -10971,7 +10971,7 @@
         <v>12</v>
       </c>
       <c r="Z34" s="17" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AA34" s="17" t="n">
         <v>19</v>
@@ -10992,7 +10992,7 @@
         <v>19</v>
       </c>
       <c r="AG34" s="17" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35" ht="24" customHeight="1">
@@ -11110,127 +11110,127 @@
       </c>
       <c r="E36" s="17" t="inlineStr">
         <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="F36" s="17" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="G36" s="17" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="H36" s="17" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="I36" s="17" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="J36" s="17" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="K36" s="17" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="L36" s="17" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="M36" s="17" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="N36" s="17" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="Q36" s="17" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="R36" s="17" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="S36" s="17" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="T36" s="17" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="U36" s="17" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="X36" s="17" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F36" s="17" t="inlineStr">
+      <c r="Y36" s="17" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G36" s="17" t="inlineStr">
+      <c r="Z36" s="17" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H36" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I36" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J36" s="17" t="inlineStr">
-        <is>
-          <t>月</t>
-        </is>
-      </c>
-      <c r="K36" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L36" s="17" t="inlineStr">
+      <c r="AA36" s="17" t="inlineStr">
         <is>
           <t>火</t>
         </is>
       </c>
-      <c r="M36" s="17" t="inlineStr">
+      <c r="AB36" s="17" t="inlineStr">
         <is>
           <t>土</t>
         </is>
       </c>
-      <c r="N36" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q36" s="17" t="inlineStr">
-        <is>
-          <t>火</t>
-        </is>
-      </c>
-      <c r="R36" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S36" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T36" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U36" s="17" t="inlineStr">
-        <is>
-          <t>土</t>
-        </is>
-      </c>
-      <c r="X36" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y36" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z36" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA36" s="17" t="inlineStr">
-        <is>
-          <t>土</t>
-        </is>
-      </c>
-      <c r="AB36" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="AC36" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>金</t>
         </is>
       </c>
       <c r="AD36" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>金</t>
         </is>
       </c>
       <c r="AE36" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>木</t>
         </is>
       </c>
       <c r="AF36" s="17" t="inlineStr">
         <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="AG36" s="17" t="inlineStr">
+        <is>
           <t>水</t>
-        </is>
-      </c>
-      <c r="AG36" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
         </is>
       </c>
     </row>
@@ -11415,42 +11415,42 @@
       </c>
       <c r="Z2" s="7" t="inlineStr">
         <is>
+          <t>岡本</t>
+        </is>
+      </c>
+      <c r="AA2" s="7" t="inlineStr">
+        <is>
           <t>石渡</t>
         </is>
       </c>
-      <c r="AA2" s="7" t="inlineStr">
+      <c r="AB2" s="7" t="inlineStr">
         <is>
           <t>今川</t>
         </is>
       </c>
-      <c r="AB2" s="7" t="inlineStr">
+      <c r="AC2" s="7" t="inlineStr">
         <is>
           <t>野田</t>
         </is>
       </c>
-      <c r="AC2" s="7" t="inlineStr">
+      <c r="AD2" s="7" t="inlineStr">
         <is>
           <t>岸</t>
         </is>
       </c>
-      <c r="AD2" s="7" t="inlineStr">
+      <c r="AE2" s="7" t="inlineStr">
         <is>
           <t>鹿島</t>
         </is>
       </c>
-      <c r="AE2" s="7" t="inlineStr">
+      <c r="AF2" s="7" t="inlineStr">
         <is>
           <t>分部</t>
         </is>
       </c>
-      <c r="AF2" s="7" t="inlineStr">
+      <c r="AG2" s="7" t="inlineStr">
         <is>
           <t>太田</t>
-        </is>
-      </c>
-      <c r="AG2" s="7" t="inlineStr">
-        <is>
-          <t>岡本</t>
         </is>
       </c>
       <c r="AH2" s="5" t="inlineStr">
@@ -11482,9 +11482,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="G3" s="8" t="inlineStr">
@@ -11522,9 +11522,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="N3" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="N3" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="O3" s="8">
@@ -11541,14 +11541,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S3" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S3" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="T3" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="U3" s="8" t="inlineStr">
@@ -11570,9 +11570,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="Z3" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z3" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AA3" s="8" t="inlineStr">
@@ -11590,9 +11590,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AD3" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AD3" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AE3" s="8" t="inlineStr">
@@ -11605,9 +11605,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AG3" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AG3" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AH3" s="8">
@@ -11641,9 +11641,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="F4" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="G4" s="15" t="inlineStr">
@@ -11666,9 +11666,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K4" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="K4" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="L4" s="15" t="inlineStr">
@@ -11681,9 +11681,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="N4" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="N4" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="O4" s="8">
@@ -11695,19 +11695,19 @@
           <t>○</t>
         </is>
       </c>
-      <c r="R4" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="S4" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T4" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="R4" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="S4" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="T4" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="U4" s="15" t="inlineStr">
@@ -11729,14 +11729,14 @@
           <t>公</t>
         </is>
       </c>
-      <c r="Z4" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AA4" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z4" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="AA4" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AB4" s="15" t="inlineStr">
@@ -11759,14 +11759,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AF4" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AG4" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AF4" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AG4" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AH4" s="8">
@@ -11791,9 +11791,9 @@
       </c>
       <c r="C5" s="9" t="inlineStr"/>
       <c r="D5" s="10" t="inlineStr"/>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
@@ -11826,9 +11826,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="L5" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="L5" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="M5" s="8" t="inlineStr">
@@ -11855,9 +11855,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S5" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S5" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="T5" s="8" t="inlineStr">
@@ -11865,9 +11865,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="U5" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="V5" s="8">
@@ -11909,9 +11909,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AE5" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AE5" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AF5" s="8" t="inlineStr">
@@ -11919,9 +11919,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AG5" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AG5" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AH5" s="8">
@@ -11965,9 +11965,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="H6" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="I6" s="15" t="inlineStr">
@@ -11980,9 +11980,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K6" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="K6" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="L6" s="15" t="inlineStr">
@@ -12009,14 +12009,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="R6" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="S6" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="R6" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="S6" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="T6" s="15" t="inlineStr">
@@ -12053,9 +12053,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB6" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AB6" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AC6" s="15" t="inlineStr">
@@ -12068,14 +12068,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AE6" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AF6" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AE6" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="AF6" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AG6" s="15" t="inlineStr">
@@ -12120,9 +12120,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H7" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="I7" s="8" t="inlineStr">
@@ -12198,19 +12198,19 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Z7" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AA7" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AB7" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z7" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="AA7" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AB7" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AC7" s="8" t="inlineStr">
@@ -12233,9 +12233,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AG7" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AG7" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AH7" s="8">
@@ -12403,9 +12403,9 @@
       </c>
       <c r="C9" s="9" t="inlineStr"/>
       <c r="D9" s="10" t="inlineStr"/>
-      <c r="E9" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
@@ -12438,9 +12438,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="L9" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="L9" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="M9" s="8" t="inlineStr">
@@ -12472,14 +12472,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="U9" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="T9" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="U9" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="V9" s="8">
@@ -12496,9 +12496,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Z9" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="Z9" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AA9" s="8" t="inlineStr">
@@ -12516,9 +12516,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AD9" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AD9" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AE9" s="8" t="inlineStr">
@@ -12563,9 +12563,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="F10" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
@@ -12603,9 +12603,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="N10" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="N10" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="O10" s="8">
@@ -12622,14 +12622,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S10" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S10" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="T10" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="U10" s="8" t="inlineStr">
@@ -12651,9 +12651,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="Z10" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z10" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AA10" s="8" t="inlineStr">
@@ -12671,9 +12671,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AD10" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AD10" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AE10" s="8" t="inlineStr">
@@ -12686,9 +12686,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AG10" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AG10" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AH10" s="8">
@@ -12718,9 +12718,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F11" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
@@ -12743,9 +12743,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K11" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="K11" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="L11" s="8" t="inlineStr">
@@ -12758,9 +12758,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="N11" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="N11" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="O11" s="8">
@@ -12772,19 +12772,19 @@
           <t>○</t>
         </is>
       </c>
-      <c r="R11" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="S11" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T11" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="R11" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="S11" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="U11" s="8" t="inlineStr">
@@ -12806,14 +12806,14 @@
           <t>公</t>
         </is>
       </c>
-      <c r="Z11" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AA11" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z11" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="AA11" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AB11" s="8" t="inlineStr">
@@ -12836,14 +12836,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AF11" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AG11" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AF11" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AG11" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AH11" s="8">
@@ -12868,9 +12868,9 @@
       </c>
       <c r="C12" s="9" t="inlineStr"/>
       <c r="D12" s="10" t="inlineStr"/>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
@@ -12903,9 +12903,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="L12" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="L12" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="M12" s="8" t="inlineStr">
@@ -12937,14 +12937,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="T12" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="U12" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="V12" s="8">
@@ -12986,9 +12986,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AE12" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AE12" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AF12" s="8" t="inlineStr">
@@ -12996,9 +12996,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AG12" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AG12" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AH12" s="8">
@@ -13042,9 +13042,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="H13" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="H13" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="I13" s="15" t="inlineStr">
@@ -13057,9 +13057,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K13" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="K13" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="L13" s="15" t="inlineStr">
@@ -13086,14 +13086,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="R13" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="S13" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="R13" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="S13" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="T13" s="15" t="inlineStr">
@@ -13130,9 +13130,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB13" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AB13" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AC13" s="15" t="inlineStr">
@@ -13145,14 +13145,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AE13" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AF13" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AE13" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="AF13" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AG13" s="15" t="inlineStr">
@@ -13197,9 +13197,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H14" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="I14" s="8" t="inlineStr">
@@ -13275,19 +13275,19 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Z14" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AA14" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AB14" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z14" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="AA14" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AB14" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AC14" s="8" t="inlineStr">
@@ -13310,9 +13310,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AG14" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AG14" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AH14" s="8">
@@ -13480,9 +13480,9 @@
       </c>
       <c r="C16" s="9" t="inlineStr"/>
       <c r="D16" s="10" t="inlineStr"/>
-      <c r="E16" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
@@ -13515,9 +13515,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="L16" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="L16" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="M16" s="8" t="inlineStr">
@@ -13544,9 +13544,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S16" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S16" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="T16" s="11" t="inlineStr">
@@ -13573,9 +13573,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Z16" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="Z16" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AA16" s="8" t="inlineStr">
@@ -13593,9 +13593,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AD16" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AD16" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AE16" s="8" t="inlineStr">
@@ -13644,9 +13644,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F17" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="F17" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="G17" s="15" t="inlineStr">
@@ -13684,9 +13684,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="N17" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="N17" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="O17" s="8">
@@ -13708,9 +13708,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="T17" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="T17" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="U17" s="15" t="inlineStr">
@@ -13732,9 +13732,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="Z17" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z17" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AA17" s="15" t="inlineStr">
@@ -13752,14 +13752,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AD17" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AE17" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AD17" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="AE17" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AF17" s="15" t="inlineStr">
@@ -13767,9 +13767,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AG17" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AG17" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AH17" s="8">
@@ -13799,9 +13799,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="G18" s="8" t="inlineStr">
@@ -13814,9 +13814,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="I18" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="I18" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="J18" s="8" t="inlineStr">
@@ -13824,9 +13824,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K18" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="K18" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="L18" s="8" t="inlineStr">
@@ -13839,9 +13839,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="N18" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="N18" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="O18" s="8">
@@ -13853,9 +13853,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="R18" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="R18" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="S18" s="11" t="inlineStr">
@@ -13868,9 +13868,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="U18" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="V18" s="8">
@@ -13887,14 +13887,14 @@
           <t>公</t>
         </is>
       </c>
-      <c r="Z18" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AA18" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z18" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="AA18" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AB18" s="8" t="inlineStr">
@@ -13917,14 +13917,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AF18" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AG18" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AF18" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AG18" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AH18" s="8">
@@ -13949,9 +13949,9 @@
       </c>
       <c r="C19" s="9" t="inlineStr"/>
       <c r="D19" s="10" t="inlineStr"/>
-      <c r="E19" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
@@ -13969,9 +13969,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="I19" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="I19" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="J19" s="8" t="inlineStr">
@@ -13984,9 +13984,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="L19" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="L19" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="M19" s="8" t="inlineStr">
@@ -14008,14 +14008,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="R19" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="S19" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="R19" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="S19" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
@@ -14023,9 +14023,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="U19" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="V19" s="8">
@@ -14077,9 +14077,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AG19" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AG19" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AH19" s="8">
@@ -14123,9 +14123,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="H20" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="H20" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="I20" s="15" t="inlineStr">
@@ -14138,9 +14138,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K20" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="K20" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="L20" s="15" t="inlineStr">
@@ -14172,14 +14172,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S20" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T20" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S20" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="T20" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="U20" s="15" t="inlineStr">
@@ -14211,9 +14211,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB20" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AB20" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AC20" s="15" t="inlineStr">
@@ -14226,14 +14226,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AE20" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AF20" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AE20" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="AF20" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AG20" s="15" t="inlineStr">
@@ -14278,9 +14278,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H21" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="I21" s="8" t="inlineStr">
@@ -14356,19 +14356,19 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Z21" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AA21" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AB21" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z21" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="AA21" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AB21" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AC21" s="8" t="inlineStr">
@@ -14391,9 +14391,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AG21" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AG21" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AH21" s="8">
@@ -14561,9 +14561,9 @@
       </c>
       <c r="C23" s="9" t="inlineStr"/>
       <c r="D23" s="10" t="inlineStr"/>
-      <c r="E23" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
@@ -14596,9 +14596,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="L23" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="L23" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="M23" s="8" t="inlineStr">
@@ -14654,9 +14654,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Z23" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="Z23" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AA23" s="8" t="inlineStr">
@@ -14674,9 +14674,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AD23" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AD23" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AE23" s="8" t="inlineStr">
@@ -14721,9 +14721,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F24" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="F24" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="G24" s="8" t="inlineStr">
@@ -14761,9 +14761,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="N24" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="N24" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="O24" s="8">
@@ -14785,14 +14785,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="U24" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="T24" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="V24" s="8">
@@ -14809,9 +14809,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="Z24" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z24" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AA24" s="8" t="inlineStr">
@@ -14829,14 +14829,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AD24" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AE24" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AD24" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="AE24" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AF24" s="8" t="inlineStr">
@@ -14844,9 +14844,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AG24" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AG24" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AH24" s="8">
@@ -14876,9 +14876,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F25" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="G25" s="8" t="inlineStr">
@@ -14891,9 +14891,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="I25" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="I25" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="J25" s="8" t="inlineStr">
@@ -14901,9 +14901,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K25" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="K25" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="L25" s="8" t="inlineStr">
@@ -14916,9 +14916,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="N25" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="N25" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="O25" s="8">
@@ -14935,9 +14935,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="S25" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S25" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="T25" s="8" t="inlineStr">
@@ -14945,9 +14945,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="U25" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="V25" s="8">
@@ -14964,14 +14964,14 @@
           <t>公</t>
         </is>
       </c>
-      <c r="Z25" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AA25" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z25" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="AA25" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AB25" s="8" t="inlineStr">
@@ -14994,14 +14994,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AF25" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AG25" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AF25" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AG25" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AH25" s="8">
@@ -15026,9 +15026,9 @@
       </c>
       <c r="C26" s="9" t="inlineStr"/>
       <c r="D26" s="10" t="inlineStr"/>
-      <c r="E26" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
@@ -15046,9 +15046,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="I26" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="I26" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="J26" s="8" t="inlineStr">
@@ -15061,9 +15061,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="L26" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="L26" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="M26" s="8" t="inlineStr">
@@ -15090,9 +15090,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S26" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S26" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="T26" s="8" t="inlineStr">
@@ -15100,9 +15100,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="U26" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="V26" s="8">
@@ -15154,9 +15154,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AG26" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AG26" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AH26" s="8">
@@ -15196,9 +15196,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="H27" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="H27" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="I27" s="8" t="inlineStr">
@@ -15211,9 +15211,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K27" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="K27" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="L27" s="8" t="inlineStr">
@@ -15245,14 +15245,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S27" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T27" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S27" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="U27" s="8" t="inlineStr">
@@ -15284,9 +15284,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB27" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AB27" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AC27" s="8" t="inlineStr">
@@ -15299,14 +15299,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AE27" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AF27" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AE27" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="AF27" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AG27" s="8" t="inlineStr">
@@ -15351,9 +15351,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H28" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="I28" s="8" t="inlineStr">
@@ -15429,19 +15429,19 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Z28" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AA28" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AB28" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z28" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="AA28" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AB28" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AC28" s="8" t="inlineStr">
@@ -15464,9 +15464,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AG28" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AG28" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AH28" s="8">
@@ -15634,9 +15634,9 @@
       </c>
       <c r="C30" s="9" t="inlineStr"/>
       <c r="D30" s="10" t="inlineStr"/>
-      <c r="E30" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr">
@@ -15669,9 +15669,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="L30" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="L30" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="M30" s="8" t="inlineStr">
@@ -15698,9 +15698,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S30" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S30" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="T30" s="11" t="inlineStr">
@@ -15727,9 +15727,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Z30" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="Z30" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AA30" s="8" t="inlineStr">
@@ -15747,9 +15747,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AD30" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AD30" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AE30" s="8" t="inlineStr">
@@ -15788,7 +15788,11 @@
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr"/>
-      <c r="D31" s="10" t="inlineStr"/>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
           <t>特有</t>
@@ -15943,7 +15947,11 @@
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr"/>
-      <c r="D32" s="10" t="inlineStr"/>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
           <t>特有</t>
@@ -16098,7 +16106,11 @@
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr"/>
-      <c r="D33" s="10" t="inlineStr"/>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
           <t>特有</t>
@@ -16406,7 +16418,7 @@
         <v>12</v>
       </c>
       <c r="Z35" s="17" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AA35" s="17" t="n">
         <v>20</v>
@@ -16427,7 +16439,7 @@
         <v>20</v>
       </c>
       <c r="AG35" s="17" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36" ht="24" customHeight="1">
@@ -16545,127 +16557,127 @@
       </c>
       <c r="E37" s="17" t="inlineStr">
         <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="F37" s="17" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="G37" s="17" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="H37" s="17" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="I37" s="17" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="J37" s="17" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="K37" s="17" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="L37" s="17" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="M37" s="17" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="N37" s="17" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="Q37" s="17" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="R37" s="17" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="S37" s="17" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="T37" s="17" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="U37" s="17" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="X37" s="17" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F37" s="17" t="inlineStr">
+      <c r="Y37" s="17" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G37" s="17" t="inlineStr">
+      <c r="Z37" s="17" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H37" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I37" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J37" s="17" t="inlineStr">
-        <is>
-          <t>月</t>
-        </is>
-      </c>
-      <c r="K37" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L37" s="17" t="inlineStr">
+      <c r="AA37" s="17" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="AB37" s="17" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="AC37" s="17" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="AD37" s="17" t="inlineStr">
         <is>
           <t>火</t>
         </is>
       </c>
-      <c r="M37" s="17" t="inlineStr">
-        <is>
-          <t>土</t>
-        </is>
-      </c>
-      <c r="N37" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q37" s="17" t="inlineStr">
-        <is>
-          <t>火</t>
-        </is>
-      </c>
-      <c r="R37" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S37" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T37" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U37" s="17" t="inlineStr">
-        <is>
-          <t>土</t>
-        </is>
-      </c>
-      <c r="X37" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y37" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z37" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA37" s="17" t="inlineStr">
-        <is>
-          <t>土</t>
-        </is>
-      </c>
-      <c r="AB37" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AC37" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD37" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="AE37" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>金</t>
         </is>
       </c>
       <c r="AF37" s="17" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>金</t>
         </is>
       </c>
       <c r="AG37" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>木</t>
         </is>
       </c>
     </row>

--- a/26年10-12月シフト.xlsx
+++ b/26年10-12月シフト.xlsx
@@ -863,14 +863,14 @@
           <t>公</t>
         </is>
       </c>
-      <c r="T3" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="U3" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="U3" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="V3" s="8">
@@ -892,9 +892,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AA3" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AA3" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AB3" s="8" t="inlineStr">
@@ -907,9 +907,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AD3" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AD3" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AE3" s="8" t="inlineStr">
@@ -954,19 +954,19 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="G4" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="H4" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H4" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="I4" s="8" t="inlineStr">
@@ -979,9 +979,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K4" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="K4" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="L4" s="11" t="inlineStr">
@@ -1057,9 +1057,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC4" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AC4" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AD4" s="8" t="inlineStr">
@@ -1067,9 +1067,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AE4" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AE4" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AF4" s="11" t="inlineStr">
@@ -1119,9 +1119,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H5" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="I5" s="8" t="inlineStr">
@@ -1149,18 +1149,18 @@
           <t>公</t>
         </is>
       </c>
-      <c r="N5" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="N5" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="O5" s="8">
         <f>COUNTIF(E5:N5, "○")</f>
         <v/>
       </c>
-      <c r="Q5" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Q5" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="R5" s="8" t="inlineStr">
@@ -1168,9 +1168,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S5" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S5" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="T5" s="8" t="inlineStr">
@@ -1475,9 +1475,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="T7" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="U7" s="8" t="inlineStr">
@@ -1504,9 +1504,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AA7" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AA7" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AB7" s="8" t="inlineStr">
@@ -1519,14 +1519,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AD7" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AE7" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AD7" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="AE7" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AF7" s="8" t="inlineStr">
@@ -1630,14 +1630,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="U8" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="T8" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="V8" s="8">
@@ -1679,9 +1679,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AE8" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AE8" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AF8" s="8" t="inlineStr">
@@ -1721,19 +1721,19 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="H9" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="F9" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="G9" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="I9" s="8" t="inlineStr">
@@ -1746,9 +1746,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K9" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="K9" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="L9" s="8" t="inlineStr">
@@ -1780,14 +1780,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S9" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T9" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S9" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="U9" s="8" t="inlineStr">
@@ -1824,9 +1824,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC9" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AC9" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AD9" s="8" t="inlineStr">
@@ -1945,9 +1945,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="U10" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="V10" s="8">
@@ -1969,9 +1969,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AA10" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AA10" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AB10" s="8" t="inlineStr">
@@ -1984,9 +1984,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AD10" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AD10" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AE10" s="8" t="inlineStr">
@@ -2035,19 +2035,19 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F11" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="G11" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="H11" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="F11" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="G11" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H11" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="I11" s="15" t="inlineStr">
@@ -2060,9 +2060,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K11" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="K11" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="L11" s="15" t="inlineStr">
@@ -2099,9 +2099,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="T11" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="T11" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="U11" s="15" t="inlineStr">
@@ -2138,9 +2138,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC11" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AC11" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AD11" s="15" t="inlineStr">
@@ -2148,9 +2148,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AE11" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AE11" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AF11" s="11" t="inlineStr">
@@ -2190,9 +2190,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="F12" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
@@ -2230,9 +2230,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="N12" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="N12" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="O12" s="8">
@@ -2699,14 +2699,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="U15" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="T15" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="V15" s="8">
@@ -2728,9 +2728,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="AA15" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AA15" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AB15" s="8" t="inlineStr">
@@ -2748,9 +2748,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AE15" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AE15" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AF15" s="8" t="inlineStr">
@@ -2794,19 +2794,19 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F16" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="G16" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="H16" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="F16" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="G16" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="H16" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="I16" s="15" t="inlineStr">
@@ -2819,9 +2819,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K16" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="K16" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="L16" s="15" t="inlineStr">
@@ -2897,14 +2897,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC16" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AD16" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AC16" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AD16" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AE16" s="15" t="inlineStr">
@@ -3018,9 +3018,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="U17" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="V17" s="8">
@@ -3042,9 +3042,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AA17" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AA17" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AB17" s="8" t="inlineStr">
@@ -3057,9 +3057,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AD17" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AD17" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AE17" s="8" t="inlineStr">
@@ -3108,19 +3108,19 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="G18" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="H18" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="F18" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="G18" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H18" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="I18" s="15" t="inlineStr">
@@ -3133,9 +3133,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K18" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="K18" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="L18" s="15" t="inlineStr">
@@ -3172,9 +3172,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="T18" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="T18" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="U18" s="15" t="inlineStr">
@@ -3211,9 +3211,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC18" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AC18" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AD18" s="15" t="inlineStr">
@@ -3221,9 +3221,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AE18" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AE18" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AF18" s="11" t="inlineStr">
@@ -3654,9 +3654,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AA21" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AA21" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AB21" s="8" t="inlineStr">
@@ -3669,9 +3669,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AD21" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AD21" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AE21" s="8" t="inlineStr">
@@ -3780,14 +3780,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="U22" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="T22" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="V22" s="8">
@@ -3829,9 +3829,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AE22" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AE22" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AF22" s="8" t="inlineStr">
@@ -3871,19 +3871,19 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="G23" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="H23" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="F23" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="G23" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="I23" s="8" t="inlineStr">
@@ -3896,9 +3896,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K23" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="K23" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="L23" s="8" t="inlineStr">
@@ -3974,9 +3974,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC23" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AC23" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AD23" s="8" t="inlineStr">
@@ -4095,9 +4095,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="U24" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="V24" s="8">
@@ -4119,9 +4119,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AA24" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AA24" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AB24" s="8" t="inlineStr">
@@ -4134,9 +4134,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AD24" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AD24" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AE24" s="8" t="inlineStr">
@@ -4185,19 +4185,19 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F25" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="G25" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="H25" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="F25" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="G25" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H25" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="I25" s="15" t="inlineStr">
@@ -4210,9 +4210,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K25" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="K25" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="L25" s="15" t="inlineStr">
@@ -4249,9 +4249,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="T25" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="T25" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="U25" s="15" t="inlineStr">
@@ -4288,9 +4288,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC25" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AC25" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AD25" s="15" t="inlineStr">
@@ -4298,9 +4298,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AE25" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AE25" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AF25" s="11" t="inlineStr">
@@ -4345,9 +4345,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="G26" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="G26" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
@@ -4360,9 +4360,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="J26" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="J26" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="K26" s="8" t="inlineStr">
@@ -4399,9 +4399,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S26" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S26" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="T26" s="8" t="inlineStr">
@@ -4697,9 +4697,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S28" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S28" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="T28" s="8" t="inlineStr">
@@ -4707,9 +4707,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="U28" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="V28" s="8">
@@ -4731,9 +4731,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AA28" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AA28" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AB28" s="8" t="inlineStr">
@@ -4741,14 +4741,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC28" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AD28" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AC28" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AD28" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AE28" s="8" t="inlineStr">
@@ -4861,9 +4861,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="T29" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="T29" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="U29" s="15" t="inlineStr">
@@ -4890,9 +4890,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="AA29" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AA29" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AB29" s="15" t="inlineStr">
@@ -4910,9 +4910,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AE29" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AE29" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AF29" s="15" t="inlineStr">
@@ -4952,19 +4952,19 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F30" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="G30" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="H30" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="F30" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="G30" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="H30" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="I30" s="8" t="inlineStr">
@@ -4977,9 +4977,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K30" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="K30" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="L30" s="8" t="inlineStr">
@@ -5001,9 +5001,9 @@
         <f>COUNTIF(E30:N30, "○")</f>
         <v/>
       </c>
-      <c r="Q30" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="Q30" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="R30" s="8" t="inlineStr">
@@ -5055,14 +5055,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC30" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AD30" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AC30" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AD30" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AE30" s="8" t="inlineStr">
@@ -5200,9 +5200,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AA31" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AA31" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AB31" s="8" t="inlineStr">
@@ -5215,9 +5215,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AD31" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AD31" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AE31" s="8" t="inlineStr">
@@ -5262,19 +5262,19 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F32" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="G32" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="H32" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="G32" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H32" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="I32" s="8" t="inlineStr">
@@ -5287,9 +5287,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K32" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="K32" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="L32" s="11" t="inlineStr">
@@ -5321,14 +5321,14 @@
           <t>公</t>
         </is>
       </c>
-      <c r="S32" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T32" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S32" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="U32" s="8" t="inlineStr">
@@ -5365,9 +5365,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC32" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AC32" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AD32" s="8" t="inlineStr">
@@ -5375,9 +5375,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AE32" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AE32" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AF32" s="11" t="inlineStr">
@@ -5437,14 +5437,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="J33" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="K33" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="J33" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="K33" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="L33" s="8" t="inlineStr">
@@ -5476,14 +5476,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S33" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S33" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="T33" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="U33" s="11" t="inlineStr">
@@ -5863,112 +5863,112 @@
       </c>
       <c r="F37" s="17" t="inlineStr">
         <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="G37" s="17" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="H37" s="17" t="inlineStr">
+        <is>
           <t>金</t>
         </is>
       </c>
-      <c r="G37" s="17" t="inlineStr">
+      <c r="I37" s="17" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="J37" s="17" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="K37" s="17" t="inlineStr">
         <is>
           <t>金</t>
         </is>
       </c>
-      <c r="H37" s="17" t="inlineStr">
-        <is>
-          <t>水</t>
-        </is>
-      </c>
-      <c r="I37" s="17" t="inlineStr">
+      <c r="L37" s="17" t="inlineStr">
+        <is>
+          <t>火・月</t>
+        </is>
+      </c>
+      <c r="M37" s="17" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="N37" s="17" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="Q37" s="17" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="R37" s="17" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="S37" s="17" t="inlineStr">
         <is>
           <t>木</t>
         </is>
       </c>
-      <c r="J37" s="17" t="inlineStr">
+      <c r="T37" s="17" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="U37" s="17" t="inlineStr">
+        <is>
+          <t>土・木</t>
+        </is>
+      </c>
+      <c r="X37" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y37" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z37" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA37" s="17" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="AB37" s="17" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="AC37" s="17" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="AD37" s="17" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="K37" s="17" t="inlineStr">
-        <is>
-          <t>水</t>
-        </is>
-      </c>
-      <c r="L37" s="17" t="inlineStr">
+      <c r="AE37" s="17" t="inlineStr">
         <is>
           <t>火</t>
-        </is>
-      </c>
-      <c r="M37" s="17" t="inlineStr">
-        <is>
-          <t>土</t>
-        </is>
-      </c>
-      <c r="N37" s="17" t="inlineStr">
-        <is>
-          <t>火</t>
-        </is>
-      </c>
-      <c r="Q37" s="17" t="inlineStr">
-        <is>
-          <t>火</t>
-        </is>
-      </c>
-      <c r="R37" s="17" t="inlineStr">
-        <is>
-          <t>金</t>
-        </is>
-      </c>
-      <c r="S37" s="17" t="inlineStr">
-        <is>
-          <t>木</t>
-        </is>
-      </c>
-      <c r="T37" s="17" t="inlineStr">
-        <is>
-          <t>金</t>
-        </is>
-      </c>
-      <c r="U37" s="17" t="inlineStr">
-        <is>
-          <t>土</t>
-        </is>
-      </c>
-      <c r="X37" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y37" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z37" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA37" s="17" t="inlineStr">
-        <is>
-          <t>月</t>
-        </is>
-      </c>
-      <c r="AB37" s="17" t="inlineStr">
-        <is>
-          <t>土</t>
-        </is>
-      </c>
-      <c r="AC37" s="17" t="inlineStr">
-        <is>
-          <t>水</t>
-        </is>
-      </c>
-      <c r="AD37" s="17" t="inlineStr">
-        <is>
-          <t>木</t>
-        </is>
-      </c>
-      <c r="AE37" s="17" t="inlineStr">
-        <is>
-          <t>金</t>
         </is>
       </c>
       <c r="AF37" s="17" t="inlineStr">
@@ -6368,9 +6368,9 @@
       </c>
       <c r="C4" s="9" t="inlineStr"/>
       <c r="D4" s="10" t="inlineStr"/>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
@@ -6403,9 +6403,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="L4" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="L4" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="M4" s="8" t="inlineStr">
@@ -6442,9 +6442,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="U4" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="U4" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="V4" s="8">
@@ -6466,9 +6466,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AA4" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AA4" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AB4" s="8" t="inlineStr">
@@ -6476,9 +6476,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC4" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AC4" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AD4" s="8" t="inlineStr">
@@ -6679,19 +6679,19 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="G6" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="H6" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="F6" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="G6" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="I6" s="15" t="inlineStr">
@@ -6704,9 +6704,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K6" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="K6" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="L6" s="15" t="inlineStr">
@@ -6738,9 +6738,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S6" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S6" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="T6" s="15" t="inlineStr">
@@ -6829,14 +6829,14 @@
       </c>
       <c r="C7" s="9" t="inlineStr"/>
       <c r="D7" s="10" t="inlineStr"/>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
@@ -6844,9 +6844,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H7" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="I7" s="8" t="inlineStr">
@@ -6864,9 +6864,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="L7" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="L7" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="M7" s="8" t="inlineStr">
@@ -6898,14 +6898,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="U7" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="T7" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="V7" s="8">
@@ -6998,9 +6998,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="G8" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="H8" s="15" t="inlineStr">
@@ -7018,9 +7018,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K8" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="K8" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="L8" s="15" t="inlineStr">
@@ -7086,9 +7086,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AA8" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AA8" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AB8" s="15" t="inlineStr">
@@ -7096,9 +7096,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC8" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AC8" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AD8" s="11" t="inlineStr">
@@ -7476,9 +7476,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="L11" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="L11" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="M11" s="8" t="inlineStr">
@@ -7510,14 +7510,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="T11" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="U11" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="V11" s="8">
@@ -7596,9 +7596,9 @@
       </c>
       <c r="C12" s="9" t="inlineStr"/>
       <c r="D12" s="10" t="inlineStr"/>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
@@ -7660,14 +7660,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S12" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S12" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="T12" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="U12" s="8" t="inlineStr">
@@ -7694,9 +7694,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="AA12" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AA12" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AB12" s="8" t="inlineStr">
@@ -7704,9 +7704,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC12" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AC12" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AD12" s="8" t="inlineStr">
@@ -7756,19 +7756,19 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F13" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="G13" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="H13" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H13" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="I13" s="8" t="inlineStr">
@@ -7781,9 +7781,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K13" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="K13" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="L13" s="8" t="inlineStr">
@@ -7815,14 +7815,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S13" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T13" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S13" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="U13" s="8" t="inlineStr">
@@ -7906,14 +7906,14 @@
       </c>
       <c r="C14" s="9" t="inlineStr"/>
       <c r="D14" s="10" t="inlineStr"/>
-      <c r="E14" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F14" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="G14" s="8" t="inlineStr">
@@ -7921,9 +7921,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H14" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="I14" s="8" t="inlineStr">
@@ -7941,9 +7941,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="L14" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="L14" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="M14" s="8" t="inlineStr">
@@ -7975,14 +7975,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="U14" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="T14" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="V14" s="8">
@@ -8075,9 +8075,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="G15" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="H15" s="15" t="inlineStr">
@@ -8095,9 +8095,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K15" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="K15" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="L15" s="15" t="inlineStr">
@@ -8163,9 +8163,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AA15" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AA15" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AB15" s="15" t="inlineStr">
@@ -8173,9 +8173,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC15" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AC15" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AD15" s="11" t="inlineStr">
@@ -8284,14 +8284,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S16" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S16" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="T16" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="U16" s="11" t="inlineStr">
@@ -8553,9 +8553,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="L18" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="L18" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="M18" s="8" t="inlineStr">
@@ -8587,14 +8587,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="T18" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="U18" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="V18" s="8">
@@ -8673,9 +8673,9 @@
       </c>
       <c r="C19" s="9" t="inlineStr"/>
       <c r="D19" s="10" t="inlineStr"/>
-      <c r="E19" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
@@ -8771,9 +8771,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="AA19" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AA19" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AB19" s="8" t="inlineStr">
@@ -8781,9 +8781,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC19" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AC19" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AD19" s="8" t="inlineStr">
@@ -8837,19 +8837,19 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F20" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="G20" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="H20" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="F20" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="G20" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H20" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="I20" s="15" t="inlineStr">
@@ -8862,9 +8862,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K20" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="K20" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="L20" s="15" t="inlineStr">
@@ -8896,14 +8896,14 @@
           <t>特有</t>
         </is>
       </c>
-      <c r="S20" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T20" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S20" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="T20" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="U20" s="15" t="inlineStr">
@@ -8987,14 +8987,14 @@
       </c>
       <c r="C21" s="9" t="inlineStr"/>
       <c r="D21" s="10" t="inlineStr"/>
-      <c r="E21" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr">
@@ -9002,9 +9002,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H21" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="I21" s="8" t="inlineStr">
@@ -9022,9 +9022,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="L21" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="L21" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="M21" s="8" t="inlineStr">
@@ -9056,14 +9056,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="U21" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="T21" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="V21" s="8">
@@ -9156,9 +9156,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="G22" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="G22" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="H22" s="15" t="inlineStr">
@@ -9176,9 +9176,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K22" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="K22" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="L22" s="15" t="inlineStr">
@@ -9244,9 +9244,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AA22" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AA22" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AB22" s="15" t="inlineStr">
@@ -9254,9 +9254,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC22" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AC22" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AD22" s="11" t="inlineStr">
@@ -9746,9 +9746,9 @@
       </c>
       <c r="C26" s="9" t="inlineStr"/>
       <c r="D26" s="10" t="inlineStr"/>
-      <c r="E26" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
@@ -9815,9 +9815,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="T26" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="U26" s="8" t="inlineStr">
@@ -9844,9 +9844,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="AA26" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AA26" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AB26" s="8" t="inlineStr">
@@ -9854,9 +9854,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC26" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AC26" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AD26" s="8" t="inlineStr">
@@ -9906,19 +9906,19 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F27" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="G27" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="H27" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H27" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="I27" s="8" t="inlineStr">
@@ -9931,9 +9931,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K27" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="K27" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="L27" s="8" t="inlineStr">
@@ -10056,14 +10056,14 @@
       </c>
       <c r="C28" s="9" t="inlineStr"/>
       <c r="D28" s="10" t="inlineStr"/>
-      <c r="E28" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="F28" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F28" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="G28" s="8" t="inlineStr">
@@ -10071,9 +10071,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H28" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="I28" s="8" t="inlineStr">
@@ -10091,9 +10091,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="L28" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="L28" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="M28" s="8" t="inlineStr">
@@ -10221,9 +10221,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="G29" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="G29" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
@@ -10241,14 +10241,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K29" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="L29" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="K29" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="L29" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="M29" s="8" t="inlineStr">
@@ -10285,9 +10285,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="U29" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="U29" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="V29" s="8">
@@ -10309,9 +10309,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AA29" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AA29" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AB29" s="8" t="inlineStr">
@@ -10319,9 +10319,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC29" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AC29" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AD29" s="11" t="inlineStr">
@@ -10420,9 +10420,9 @@
         <f>COUNTIF(E30:N30, "○")</f>
         <v/>
       </c>
-      <c r="Q30" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Q30" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="R30" s="8" t="inlineStr">
@@ -10430,9 +10430,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S30" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S30" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="T30" s="8" t="inlineStr">
@@ -10718,9 +10718,9 @@
         <f>COUNTIF(E32:N32, "○")</f>
         <v/>
       </c>
-      <c r="Q32" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="Q32" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="R32" s="8" t="inlineStr">
@@ -10738,9 +10738,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="U32" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="V32" s="8">
@@ -11110,107 +11110,107 @@
       </c>
       <c r="E36" s="17" t="inlineStr">
         <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="F36" s="17" t="inlineStr">
+        <is>
           <t>木</t>
         </is>
       </c>
-      <c r="F36" s="17" t="inlineStr">
+      <c r="G36" s="17" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="H36" s="17" t="inlineStr">
         <is>
           <t>水</t>
         </is>
       </c>
-      <c r="G36" s="17" t="inlineStr">
+      <c r="I36" s="17" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="J36" s="17" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="K36" s="17" t="inlineStr">
         <is>
           <t>水</t>
         </is>
       </c>
-      <c r="H36" s="17" t="inlineStr">
+      <c r="L36" s="17" t="inlineStr">
+        <is>
+          <t>火・木</t>
+        </is>
+      </c>
+      <c r="M36" s="17" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="N36" s="17" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="Q36" s="17" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="R36" s="17" t="inlineStr">
         <is>
           <t>木</t>
         </is>
       </c>
-      <c r="I36" s="17" t="inlineStr">
+      <c r="S36" s="17" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="T36" s="17" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="U36" s="17" t="inlineStr">
+        <is>
+          <t>土・月</t>
+        </is>
+      </c>
+      <c r="X36" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y36" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z36" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA36" s="17" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="AB36" s="17" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="AC36" s="17" t="inlineStr">
         <is>
           <t>火</t>
-        </is>
-      </c>
-      <c r="J36" s="17" t="inlineStr">
-        <is>
-          <t>月</t>
-        </is>
-      </c>
-      <c r="K36" s="17" t="inlineStr">
-        <is>
-          <t>金</t>
-        </is>
-      </c>
-      <c r="L36" s="17" t="inlineStr">
-        <is>
-          <t>火</t>
-        </is>
-      </c>
-      <c r="M36" s="17" t="inlineStr">
-        <is>
-          <t>土</t>
-        </is>
-      </c>
-      <c r="N36" s="17" t="inlineStr">
-        <is>
-          <t>金</t>
-        </is>
-      </c>
-      <c r="Q36" s="17" t="inlineStr">
-        <is>
-          <t>火</t>
-        </is>
-      </c>
-      <c r="R36" s="17" t="inlineStr">
-        <is>
-          <t>木</t>
-        </is>
-      </c>
-      <c r="S36" s="17" t="inlineStr">
-        <is>
-          <t>金</t>
-        </is>
-      </c>
-      <c r="T36" s="17" t="inlineStr">
-        <is>
-          <t>月</t>
-        </is>
-      </c>
-      <c r="U36" s="17" t="inlineStr">
-        <is>
-          <t>土</t>
-        </is>
-      </c>
-      <c r="X36" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y36" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z36" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA36" s="17" t="inlineStr">
-        <is>
-          <t>火</t>
-        </is>
-      </c>
-      <c r="AB36" s="17" t="inlineStr">
-        <is>
-          <t>土</t>
-        </is>
-      </c>
-      <c r="AC36" s="17" t="inlineStr">
-        <is>
-          <t>金</t>
         </is>
       </c>
       <c r="AD36" s="17" t="inlineStr">
@@ -11482,14 +11482,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="G3" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="G3" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="H3" s="8" t="inlineStr">
@@ -11507,9 +11507,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="K3" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="L3" s="11" t="inlineStr">
@@ -11541,14 +11541,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S3" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T3" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S3" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="U3" s="8" t="inlineStr">
@@ -11575,9 +11575,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="AA3" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AA3" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AB3" s="8" t="inlineStr">
@@ -11590,9 +11590,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AD3" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AD3" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AE3" s="8" t="inlineStr">
@@ -11666,14 +11666,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K4" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="L4" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="K4" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="L4" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="M4" s="15" t="inlineStr">
@@ -11700,9 +11700,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="S4" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S4" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="T4" s="15" t="inlineStr">
@@ -11734,9 +11734,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="AA4" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AA4" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AB4" s="15" t="inlineStr">
@@ -11759,9 +11759,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AF4" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AF4" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AG4" s="15" t="inlineStr">
@@ -11855,9 +11855,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S5" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S5" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="T5" s="8" t="inlineStr">
@@ -11899,14 +11899,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC5" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AD5" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AC5" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AD5" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AE5" s="8" t="inlineStr">
@@ -11955,14 +11955,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F6" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="G6" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="F6" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="G6" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="H6" s="11" t="inlineStr">
@@ -12014,14 +12014,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S6" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="T6" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S6" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="T6" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="U6" s="15" t="inlineStr">
@@ -12058,9 +12058,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC6" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AC6" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AD6" s="15" t="inlineStr">
@@ -12073,9 +12073,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="AF6" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AF6" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AG6" s="15" t="inlineStr">
@@ -12438,9 +12438,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="L9" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="L9" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="M9" s="8" t="inlineStr">
@@ -12563,14 +12563,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
@@ -12588,9 +12588,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K10" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="K10" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="L10" s="11" t="inlineStr">
@@ -12622,14 +12622,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S10" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T10" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S10" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="U10" s="8" t="inlineStr">
@@ -12656,9 +12656,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="AA10" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AA10" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AB10" s="8" t="inlineStr">
@@ -12671,9 +12671,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AD10" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AD10" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AE10" s="8" t="inlineStr">
@@ -12743,14 +12743,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K11" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="L11" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="K11" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="L11" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="M11" s="8" t="inlineStr">
@@ -12777,9 +12777,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="S11" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S11" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="T11" s="8" t="inlineStr">
@@ -12787,9 +12787,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="U11" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="V11" s="8">
@@ -12811,9 +12811,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="AA11" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AA11" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AB11" s="8" t="inlineStr">
@@ -12836,9 +12836,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AF11" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AF11" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AG11" s="8" t="inlineStr">
@@ -12932,9 +12932,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S12" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S12" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="T12" s="8" t="inlineStr">
@@ -12942,9 +12942,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="U12" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="U12" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="V12" s="8">
@@ -12976,14 +12976,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC12" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AD12" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AC12" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AD12" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AE12" s="8" t="inlineStr">
@@ -13032,14 +13032,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F13" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="G13" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="F13" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="G13" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="H13" s="11" t="inlineStr">
@@ -13091,14 +13091,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S13" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="T13" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S13" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="T13" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="U13" s="15" t="inlineStr">
@@ -13135,9 +13135,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC13" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AC13" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AD13" s="15" t="inlineStr">
@@ -13150,9 +13150,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="AF13" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AF13" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AG13" s="15" t="inlineStr">
@@ -13515,9 +13515,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="L16" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="L16" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="M16" s="8" t="inlineStr">
@@ -13644,14 +13644,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F17" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="G17" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="F17" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="G17" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="H17" s="15" t="inlineStr">
@@ -13669,9 +13669,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K17" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="K17" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="L17" s="11" t="inlineStr">
@@ -13703,14 +13703,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S17" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T17" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S17" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="T17" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="U17" s="15" t="inlineStr">
@@ -13737,9 +13737,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="AA17" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AA17" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AB17" s="15" t="inlineStr">
@@ -13752,9 +13752,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AD17" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AD17" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AE17" s="15" t="inlineStr">
@@ -13824,14 +13824,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K18" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="L18" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="K18" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="L18" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="M18" s="8" t="inlineStr">
@@ -13858,9 +13858,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="S18" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S18" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="T18" s="8" t="inlineStr">
@@ -13868,9 +13868,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="U18" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="V18" s="8">
@@ -13892,9 +13892,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="AA18" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AA18" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AB18" s="8" t="inlineStr">
@@ -13917,9 +13917,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AF18" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AF18" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AG18" s="8" t="inlineStr">
@@ -14013,9 +14013,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S19" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S19" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
@@ -14023,9 +14023,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="U19" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="V19" s="8">
@@ -14057,14 +14057,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC19" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AD19" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AC19" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AD19" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AE19" s="8" t="inlineStr">
@@ -14113,14 +14113,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F20" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="G20" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="F20" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="G20" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="H20" s="11" t="inlineStr">
@@ -14172,14 +14172,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S20" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="T20" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S20" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="T20" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="U20" s="15" t="inlineStr">
@@ -14216,9 +14216,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC20" s="15" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AC20" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AD20" s="15" t="inlineStr">
@@ -14231,9 +14231,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="AF20" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AF20" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AG20" s="15" t="inlineStr">
@@ -14596,9 +14596,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="L23" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="L23" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="M23" s="8" t="inlineStr">
@@ -14721,14 +14721,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F24" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="G24" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="G24" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
@@ -14746,9 +14746,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K24" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="K24" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="L24" s="11" t="inlineStr">
@@ -14780,14 +14780,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S24" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T24" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S24" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="U24" s="8" t="inlineStr">
@@ -14814,9 +14814,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="AA24" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AA24" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AB24" s="8" t="inlineStr">
@@ -14829,9 +14829,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AD24" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AD24" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AE24" s="8" t="inlineStr">
@@ -14901,14 +14901,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K25" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="L25" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="K25" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="L25" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="M25" s="8" t="inlineStr">
@@ -14935,9 +14935,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="S25" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S25" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="T25" s="8" t="inlineStr">
@@ -14945,9 +14945,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="U25" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="V25" s="8">
@@ -14969,9 +14969,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="AA25" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AA25" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AB25" s="8" t="inlineStr">
@@ -14994,9 +14994,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AF25" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AF25" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AG25" s="8" t="inlineStr">
@@ -15090,9 +15090,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S26" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S26" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="T26" s="8" t="inlineStr">
@@ -15100,9 +15100,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="U26" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="U26" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="V26" s="8">
@@ -15134,14 +15134,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC26" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AD26" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AC26" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AD26" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AE26" s="8" t="inlineStr">
@@ -15186,14 +15186,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F27" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="G27" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="F27" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr">
@@ -15245,14 +15245,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S27" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S27" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="T27" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="U27" s="8" t="inlineStr">
@@ -15289,9 +15289,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC27" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AC27" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AD27" s="8" t="inlineStr">
@@ -15304,9 +15304,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="AF27" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AF27" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AG27" s="8" t="inlineStr">
@@ -15669,9 +15669,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="L30" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="L30" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="M30" s="8" t="inlineStr">
@@ -16562,117 +16562,117 @@
       </c>
       <c r="F37" s="17" t="inlineStr">
         <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="G37" s="17" t="inlineStr">
+        <is>
           <t>火</t>
         </is>
       </c>
-      <c r="G37" s="17" t="inlineStr">
+      <c r="H37" s="17" t="inlineStr">
         <is>
           <t>金</t>
         </is>
       </c>
-      <c r="H37" s="17" t="inlineStr">
+      <c r="I37" s="17" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="J37" s="17" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="K37" s="17" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="L37" s="17" t="inlineStr">
+        <is>
+          <t>火・水</t>
+        </is>
+      </c>
+      <c r="M37" s="17" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="N37" s="17" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="Q37" s="17" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="R37" s="17" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="S37" s="17" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="T37" s="17" t="inlineStr">
         <is>
           <t>金</t>
         </is>
       </c>
-      <c r="I37" s="17" t="inlineStr">
+      <c r="U37" s="17" t="inlineStr">
+        <is>
+          <t>土・水</t>
+        </is>
+      </c>
+      <c r="X37" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y37" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z37" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA37" s="17" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="AB37" s="17" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="AC37" s="17" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="AD37" s="17" t="inlineStr">
         <is>
           <t>木</t>
         </is>
       </c>
-      <c r="J37" s="17" t="inlineStr">
-        <is>
-          <t>月</t>
-        </is>
-      </c>
-      <c r="K37" s="17" t="inlineStr">
+      <c r="AE37" s="17" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="AF37" s="17" t="inlineStr">
         <is>
           <t>水</t>
-        </is>
-      </c>
-      <c r="L37" s="17" t="inlineStr">
-        <is>
-          <t>火</t>
-        </is>
-      </c>
-      <c r="M37" s="17" t="inlineStr">
-        <is>
-          <t>土</t>
-        </is>
-      </c>
-      <c r="N37" s="17" t="inlineStr">
-        <is>
-          <t>水</t>
-        </is>
-      </c>
-      <c r="Q37" s="17" t="inlineStr">
-        <is>
-          <t>火</t>
-        </is>
-      </c>
-      <c r="R37" s="17" t="inlineStr">
-        <is>
-          <t>水</t>
-        </is>
-      </c>
-      <c r="S37" s="17" t="inlineStr">
-        <is>
-          <t>水</t>
-        </is>
-      </c>
-      <c r="T37" s="17" t="inlineStr">
-        <is>
-          <t>火</t>
-        </is>
-      </c>
-      <c r="U37" s="17" t="inlineStr">
-        <is>
-          <t>土</t>
-        </is>
-      </c>
-      <c r="X37" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y37" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z37" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA37" s="17" t="inlineStr">
-        <is>
-          <t>水</t>
-        </is>
-      </c>
-      <c r="AB37" s="17" t="inlineStr">
-        <is>
-          <t>土</t>
-        </is>
-      </c>
-      <c r="AC37" s="17" t="inlineStr">
-        <is>
-          <t>木</t>
-        </is>
-      </c>
-      <c r="AD37" s="17" t="inlineStr">
-        <is>
-          <t>火</t>
-        </is>
-      </c>
-      <c r="AE37" s="17" t="inlineStr">
-        <is>
-          <t>金</t>
-        </is>
-      </c>
-      <c r="AF37" s="17" t="inlineStr">
-        <is>
-          <t>金</t>
         </is>
       </c>
       <c r="AG37" s="17" t="inlineStr">
